--- a/research/traditional_assets/database/data/philippines/philippines_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_drugs_pharmaceutical.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1065594692142295</v>
+        <v>0.1063268205411939</v>
       </c>
       <c r="C2">
-        <v>127.2045779317679</v>
+        <v>126.2997119146436</v>
       </c>
       <c r="D2">
-        <v>110.6045779317678</v>
+        <v>111.0297119146436</v>
       </c>
       <c r="E2">
-        <v>-74.90000000000001</v>
+        <v>-73.57000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="G2">
         <v>16.6</v>
@@ -1439,28 +1439,28 @@
         <v>18.375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.066899</v>
       </c>
       <c r="N2">
-        <v>18.375</v>
+        <v>18.308101</v>
       </c>
       <c r="O2">
-        <v>4.59375</v>
+        <v>4.57702525</v>
       </c>
       <c r="P2">
-        <v>13.78125</v>
+        <v>13.73107575</v>
       </c>
       <c r="Q2">
-        <v>18.28125</v>
+        <v>18.23107575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1065594692142295</v>
+        <v>0.1070197682234282</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8908222216697549</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>274.6677827770221</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1063268205411939</v>
+        <v>0.1060941718681583</v>
       </c>
       <c r="C3">
-        <v>126.2997119146436</v>
+        <v>125.3981267073859</v>
       </c>
       <c r="D3">
-        <v>111.0297119146436</v>
+        <v>111.4581267073859</v>
       </c>
       <c r="E3">
-        <v>-73.57000000000001</v>
+        <v>-72.24000000000001</v>
       </c>
       <c r="F3">
-        <v>1.33</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
         <v>16.6</v>
@@ -1521,28 +1521,28 @@
         <v>18.375</v>
       </c>
       <c r="M3">
-        <v>0.066899</v>
+        <v>0.133798</v>
       </c>
       <c r="N3">
-        <v>18.308101</v>
+        <v>18.241202</v>
       </c>
       <c r="O3">
-        <v>4.57702525</v>
+        <v>4.5603005</v>
       </c>
       <c r="P3">
-        <v>13.73107575</v>
+        <v>13.6809015</v>
       </c>
       <c r="Q3">
-        <v>18.23107575</v>
+        <v>18.1809015</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1070197682234282</v>
+        <v>0.1074894610899575</v>
       </c>
       <c r="T3">
-        <v>0.8908222216697549</v>
+        <v>0.897656825181108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>274.6677827770221</v>
+        <v>137.333891388511</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1060941718681583</v>
+        <v>0.1058615231951228</v>
       </c>
       <c r="C4">
-        <v>125.3981267073859</v>
+        <v>124.4998604347052</v>
       </c>
       <c r="D4">
-        <v>111.4581267073859</v>
+        <v>111.8898604347052</v>
       </c>
       <c r="E4">
-        <v>-72.24000000000001</v>
+        <v>-70.91000000000001</v>
       </c>
       <c r="F4">
-        <v>2.66</v>
+        <v>3.99</v>
       </c>
       <c r="G4">
         <v>16.6</v>
@@ -1603,28 +1603,28 @@
         <v>18.375</v>
       </c>
       <c r="M4">
-        <v>0.133798</v>
+        <v>0.200697</v>
       </c>
       <c r="N4">
-        <v>18.241202</v>
+        <v>18.174303</v>
       </c>
       <c r="O4">
-        <v>4.5603005</v>
+        <v>4.54357575</v>
       </c>
       <c r="P4">
-        <v>13.6809015</v>
+        <v>13.63072725</v>
       </c>
       <c r="Q4">
-        <v>18.1809015</v>
+        <v>18.13072725</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1074894610899575</v>
+        <v>0.1079688383454874</v>
       </c>
       <c r="T4">
-        <v>0.897656825181108</v>
+        <v>0.9046323483524888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>137.333891388511</v>
+        <v>91.55592759234069</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1058615231951228</v>
+        <v>0.1056288745220872</v>
       </c>
       <c r="C5">
-        <v>124.4998604347052</v>
+        <v>123.6049518143142</v>
       </c>
       <c r="D5">
-        <v>111.8898604347052</v>
+        <v>112.3249518143142</v>
       </c>
       <c r="E5">
-        <v>-70.91000000000001</v>
+        <v>-69.58000000000001</v>
       </c>
       <c r="F5">
-        <v>3.99</v>
+        <v>5.32</v>
       </c>
       <c r="G5">
         <v>16.6</v>
@@ -1685,28 +1685,28 @@
         <v>18.375</v>
       </c>
       <c r="M5">
-        <v>0.200697</v>
+        <v>0.267596</v>
       </c>
       <c r="N5">
-        <v>18.174303</v>
+        <v>18.107404</v>
       </c>
       <c r="O5">
-        <v>4.54357575</v>
+        <v>4.526851</v>
       </c>
       <c r="P5">
-        <v>13.63072725</v>
+        <v>13.580553</v>
       </c>
       <c r="Q5">
-        <v>18.13072725</v>
+        <v>18.080553</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1079688383454874</v>
+        <v>0.1084582026271741</v>
       </c>
       <c r="T5">
-        <v>0.9046323483524888</v>
+        <v>0.9117531949232736</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>91.55592759234069</v>
+        <v>68.66694569425552</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1056288745220872</v>
+        <v>0.1053962258490516</v>
       </c>
       <c r="C6">
-        <v>123.6049518143142</v>
+        <v>122.7134401685025</v>
       </c>
       <c r="D6">
-        <v>112.3249518143142</v>
+        <v>112.7634401685025</v>
       </c>
       <c r="E6">
-        <v>-69.58000000000001</v>
+        <v>-68.25</v>
       </c>
       <c r="F6">
-        <v>5.32</v>
+        <v>6.65</v>
       </c>
       <c r="G6">
         <v>16.6</v>
@@ -1767,28 +1767,28 @@
         <v>18.375</v>
       </c>
       <c r="M6">
-        <v>0.267596</v>
+        <v>0.334495</v>
       </c>
       <c r="N6">
-        <v>18.107404</v>
+        <v>18.040505</v>
       </c>
       <c r="O6">
-        <v>4.526851</v>
+        <v>4.51012625</v>
       </c>
       <c r="P6">
-        <v>13.580553</v>
+        <v>13.53037875</v>
       </c>
       <c r="Q6">
-        <v>18.080553</v>
+        <v>18.03037875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1084582026271741</v>
+        <v>0.1089578693147912</v>
       </c>
       <c r="T6">
-        <v>0.9117531949232736</v>
+        <v>0.9190239540534433</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.66694569425552</v>
+        <v>54.93355655540442</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1053962258490516</v>
+        <v>0.105163577176016</v>
       </c>
       <c r="C7">
-        <v>122.7134401685025</v>
+        <v>121.8253654359833</v>
       </c>
       <c r="D7">
-        <v>112.7634401685025</v>
+        <v>113.2053654359833</v>
       </c>
       <c r="E7">
-        <v>-68.25</v>
+        <v>-66.92</v>
       </c>
       <c r="F7">
-        <v>6.65</v>
+        <v>7.98</v>
       </c>
       <c r="G7">
         <v>16.6</v>
@@ -1849,28 +1849,28 @@
         <v>18.375</v>
       </c>
       <c r="M7">
-        <v>0.334495</v>
+        <v>0.401394</v>
       </c>
       <c r="N7">
-        <v>18.040505</v>
+        <v>17.973606</v>
       </c>
       <c r="O7">
-        <v>4.51012625</v>
+        <v>4.4934015</v>
       </c>
       <c r="P7">
-        <v>13.53037875</v>
+        <v>13.4802045</v>
       </c>
       <c r="Q7">
-        <v>18.03037875</v>
+        <v>17.9802045</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1089578693147912</v>
+        <v>0.1094681672085277</v>
       </c>
       <c r="T7">
-        <v>0.9190239540534433</v>
+        <v>0.9264494101863824</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.93355655540442</v>
+        <v>45.77796379617035</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.105163577176016</v>
+        <v>0.1049309285029804</v>
       </c>
       <c r="C8">
-        <v>121.8253654359833</v>
+        <v>120.94076818402</v>
       </c>
       <c r="D8">
-        <v>113.2053654359833</v>
+        <v>113.65076818402</v>
       </c>
       <c r="E8">
-        <v>-66.92</v>
+        <v>-65.59</v>
       </c>
       <c r="F8">
-        <v>7.98</v>
+        <v>9.309999999999999</v>
       </c>
       <c r="G8">
         <v>16.6</v>
@@ -1931,28 +1931,28 @@
         <v>18.375</v>
       </c>
       <c r="M8">
-        <v>0.401394</v>
+        <v>0.4682929999999999</v>
       </c>
       <c r="N8">
-        <v>17.973606</v>
+        <v>17.906707</v>
       </c>
       <c r="O8">
-        <v>4.4934015</v>
+        <v>4.47667675</v>
       </c>
       <c r="P8">
-        <v>13.4802045</v>
+        <v>13.43003025</v>
       </c>
       <c r="Q8">
-        <v>17.9802045</v>
+        <v>17.93003025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1094681672085277</v>
+        <v>0.1099894392505166</v>
       </c>
       <c r="T8">
-        <v>0.9264494101863824</v>
+        <v>0.9340345535479869</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.77796379617035</v>
+        <v>39.23825468243174</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1049309285029804</v>
+        <v>0.1046982798299449</v>
       </c>
       <c r="C9">
-        <v>120.9407681840201</v>
+        <v>120.05968962084</v>
       </c>
       <c r="D9">
-        <v>113.6507681840201</v>
+        <v>114.09968962084</v>
       </c>
       <c r="E9">
-        <v>-65.59</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="F9">
-        <v>9.31</v>
+        <v>10.64</v>
       </c>
       <c r="G9">
         <v>16.6</v>
@@ -2013,28 +2013,28 @@
         <v>18.375</v>
       </c>
       <c r="M9">
-        <v>0.468293</v>
+        <v>0.535192</v>
       </c>
       <c r="N9">
-        <v>17.906707</v>
+        <v>17.839808</v>
       </c>
       <c r="O9">
-        <v>4.47667675</v>
+        <v>4.459952</v>
       </c>
       <c r="P9">
-        <v>13.43003025</v>
+        <v>13.379856</v>
       </c>
       <c r="Q9">
-        <v>17.93003025</v>
+        <v>17.879856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1099894392505166</v>
+        <v>0.1105220432934184</v>
       </c>
       <c r="T9">
-        <v>0.9340345535479869</v>
+        <v>0.9417845913304961</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.23825468243172</v>
+        <v>34.33347284712777</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1046982798299449</v>
+        <v>0.1044656311569093</v>
       </c>
       <c r="C10">
-        <v>120.05968962084</v>
+        <v>119.1821716083441</v>
       </c>
       <c r="D10">
-        <v>114.09968962084</v>
+        <v>114.5521716083441</v>
       </c>
       <c r="E10">
-        <v>-64.26000000000001</v>
+        <v>-62.93000000000001</v>
       </c>
       <c r="F10">
-        <v>10.64</v>
+        <v>11.97</v>
       </c>
       <c r="G10">
         <v>16.6</v>
@@ -2095,28 +2095,28 @@
         <v>18.375</v>
       </c>
       <c r="M10">
-        <v>0.535192</v>
+        <v>0.6020909999999999</v>
       </c>
       <c r="N10">
-        <v>17.839808</v>
+        <v>17.772909</v>
       </c>
       <c r="O10">
-        <v>4.459952</v>
+        <v>4.44322725</v>
       </c>
       <c r="P10">
-        <v>13.379856</v>
+        <v>13.32968175</v>
       </c>
       <c r="Q10">
-        <v>17.879856</v>
+        <v>17.82968175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1105220432934184</v>
+        <v>0.1110663529196806</v>
       </c>
       <c r="T10">
-        <v>0.9417845913304961</v>
+        <v>0.9497049596137195</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.33347284712777</v>
+        <v>30.51864253078023</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1044656311569093</v>
+        <v>0.1042329824838737</v>
       </c>
       <c r="C11">
-        <v>119.1821716083441</v>
+        <v>118.3082566751192</v>
       </c>
       <c r="D11">
-        <v>114.5521716083441</v>
+        <v>115.0082566751192</v>
       </c>
       <c r="E11">
-        <v>-62.93000000000001</v>
+        <v>-61.60000000000001</v>
       </c>
       <c r="F11">
-        <v>11.97</v>
+        <v>13.3</v>
       </c>
       <c r="G11">
         <v>16.6</v>
@@ -2177,28 +2177,28 @@
         <v>18.375</v>
       </c>
       <c r="M11">
-        <v>0.6020909999999999</v>
+        <v>0.6689899999999999</v>
       </c>
       <c r="N11">
-        <v>17.772909</v>
+        <v>17.70601</v>
       </c>
       <c r="O11">
-        <v>4.44322725</v>
+        <v>4.4265025</v>
       </c>
       <c r="P11">
-        <v>13.32968175</v>
+        <v>13.2795075</v>
       </c>
       <c r="Q11">
-        <v>17.82968175</v>
+        <v>17.7795075</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1110663529196806</v>
+        <v>0.1116227583154153</v>
       </c>
       <c r="T11">
-        <v>0.9497049596137195</v>
+        <v>0.9578013360810146</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.51864253078023</v>
+        <v>27.46677827770221</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1042329824838737</v>
+        <v>0.1040003338108381</v>
       </c>
       <c r="C12">
-        <v>118.3082566751192</v>
+        <v>117.4379880297634</v>
       </c>
       <c r="D12">
-        <v>115.0082566751192</v>
+        <v>115.4679880297634</v>
       </c>
       <c r="E12">
-        <v>-61.60000000000001</v>
+        <v>-60.27</v>
       </c>
       <c r="F12">
-        <v>13.3</v>
+        <v>14.63</v>
       </c>
       <c r="G12">
         <v>16.6</v>
@@ -2259,28 +2259,28 @@
         <v>18.375</v>
       </c>
       <c r="M12">
-        <v>0.66899</v>
+        <v>0.735889</v>
       </c>
       <c r="N12">
-        <v>17.70601</v>
+        <v>17.639111</v>
       </c>
       <c r="O12">
-        <v>4.4265025</v>
+        <v>4.40977775</v>
       </c>
       <c r="P12">
-        <v>13.2795075</v>
+        <v>13.22933325</v>
       </c>
       <c r="Q12">
-        <v>17.7795075</v>
+        <v>17.72933325</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1116227583154153</v>
+        <v>0.1121916672031889</v>
       </c>
       <c r="T12">
-        <v>0.9578013360810146</v>
+        <v>0.9660796535925187</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.46677827770221</v>
+        <v>24.96979843427473</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1040003338108381</v>
+        <v>0.1037676851378026</v>
       </c>
       <c r="C13">
-        <v>117.4379880297634</v>
+        <v>116.5714095745318</v>
       </c>
       <c r="D13">
-        <v>115.4679880297634</v>
+        <v>115.9314095745318</v>
       </c>
       <c r="E13">
-        <v>-60.27</v>
+        <v>-58.94</v>
       </c>
       <c r="F13">
-        <v>14.63</v>
+        <v>15.96</v>
       </c>
       <c r="G13">
         <v>16.6</v>
@@ -2341,28 +2341,28 @@
         <v>18.375</v>
       </c>
       <c r="M13">
-        <v>0.735889</v>
+        <v>0.8027879999999999</v>
       </c>
       <c r="N13">
-        <v>17.639111</v>
+        <v>17.572212</v>
       </c>
       <c r="O13">
-        <v>4.40977775</v>
+        <v>4.393053</v>
       </c>
       <c r="P13">
-        <v>13.22933325</v>
+        <v>13.179159</v>
       </c>
       <c r="Q13">
-        <v>17.72933325</v>
+        <v>17.679159</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1121916672031889</v>
+        <v>0.112773505838412</v>
       </c>
       <c r="T13">
-        <v>0.9660796535925187</v>
+        <v>0.9745461146838296</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.96979843427473</v>
+        <v>22.88898189808517</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1037676851378026</v>
+        <v>0.103535036464767</v>
       </c>
       <c r="C14">
-        <v>116.5714095745318</v>
+        <v>115.7085659193125</v>
       </c>
       <c r="D14">
-        <v>115.9314095745318</v>
+        <v>116.3985659193125</v>
       </c>
       <c r="E14">
-        <v>-58.94</v>
+        <v>-57.61000000000001</v>
       </c>
       <c r="F14">
-        <v>15.96</v>
+        <v>17.29</v>
       </c>
       <c r="G14">
         <v>16.6</v>
@@ -2423,28 +2423,28 @@
         <v>18.375</v>
       </c>
       <c r="M14">
-        <v>0.8027879999999999</v>
+        <v>0.8696869999999999</v>
       </c>
       <c r="N14">
-        <v>17.572212</v>
+        <v>17.505313</v>
       </c>
       <c r="O14">
-        <v>4.393053</v>
+        <v>4.37632825</v>
       </c>
       <c r="P14">
-        <v>13.179159</v>
+        <v>13.12898475</v>
       </c>
       <c r="Q14">
-        <v>17.679159</v>
+        <v>17.62898475</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.112773505838412</v>
+        <v>0.1133687200744448</v>
       </c>
       <c r="T14">
-        <v>0.9745461146838296</v>
+        <v>0.9832072070645959</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.88898189808517</v>
+        <v>21.12829098284785</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.103535036464767</v>
+        <v>0.1033023877917314</v>
       </c>
       <c r="C15">
-        <v>115.7085659193125</v>
+        <v>114.8495023959411</v>
       </c>
       <c r="D15">
-        <v>116.3985659193125</v>
+        <v>116.8695023959411</v>
       </c>
       <c r="E15">
-        <v>-57.61000000000001</v>
+        <v>-56.28</v>
       </c>
       <c r="F15">
-        <v>17.29</v>
+        <v>18.62</v>
       </c>
       <c r="G15">
         <v>16.6</v>
@@ -2505,28 +2505,28 @@
         <v>18.375</v>
       </c>
       <c r="M15">
-        <v>0.8696869999999999</v>
+        <v>0.936586</v>
       </c>
       <c r="N15">
-        <v>17.505313</v>
+        <v>17.438414</v>
       </c>
       <c r="O15">
-        <v>4.37632825</v>
+        <v>4.3596035</v>
       </c>
       <c r="P15">
-        <v>13.12898475</v>
+        <v>13.0788105</v>
       </c>
       <c r="Q15">
-        <v>17.62898475</v>
+        <v>17.5788105</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1133687200744448</v>
+        <v>0.1139777765020133</v>
       </c>
       <c r="T15">
-        <v>0.9832072070645959</v>
+        <v>0.9920697201984033</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.12829098284785</v>
+        <v>19.61912734121587</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1033023877917314</v>
+        <v>0.1030697391186959</v>
       </c>
       <c r="C16">
-        <v>114.8495023959411</v>
+        <v>113.9942650728653</v>
       </c>
       <c r="D16">
-        <v>116.8695023959411</v>
+        <v>117.3442650728653</v>
       </c>
       <c r="E16">
-        <v>-56.28</v>
+        <v>-54.95</v>
       </c>
       <c r="F16">
-        <v>18.62</v>
+        <v>19.95</v>
       </c>
       <c r="G16">
         <v>16.6</v>
@@ -2587,28 +2587,28 @@
         <v>18.375</v>
       </c>
       <c r="M16">
-        <v>0.936586</v>
+        <v>1.003485</v>
       </c>
       <c r="N16">
-        <v>17.438414</v>
+        <v>17.371515</v>
       </c>
       <c r="O16">
-        <v>4.3596035</v>
+        <v>4.34287875</v>
       </c>
       <c r="P16">
-        <v>13.0788105</v>
+        <v>13.02863625</v>
       </c>
       <c r="Q16">
-        <v>17.5788105</v>
+        <v>17.52863625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1139777765020133</v>
+        <v>0.114601163669054</v>
       </c>
       <c r="T16">
-        <v>0.9920697201984033</v>
+        <v>1.001140763053006</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.61912734121587</v>
+        <v>18.31118551846813</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1030697391186959</v>
+        <v>0.1028370904456603</v>
       </c>
       <c r="C17">
-        <v>113.9942650728653</v>
+        <v>113.1429007701674</v>
       </c>
       <c r="D17">
-        <v>117.3442650728653</v>
+        <v>117.8229007701674</v>
       </c>
       <c r="E17">
-        <v>-54.95</v>
+        <v>-53.62</v>
       </c>
       <c r="F17">
-        <v>19.95</v>
+        <v>21.28</v>
       </c>
       <c r="G17">
         <v>16.6</v>
@@ -2669,28 +2669,28 @@
         <v>18.375</v>
       </c>
       <c r="M17">
-        <v>1.003485</v>
+        <v>1.070384</v>
       </c>
       <c r="N17">
-        <v>17.371515</v>
+        <v>17.304616</v>
       </c>
       <c r="O17">
-        <v>4.34287875</v>
+        <v>4.326154</v>
       </c>
       <c r="P17">
-        <v>13.02863625</v>
+        <v>12.978462</v>
       </c>
       <c r="Q17">
-        <v>17.52863625</v>
+        <v>17.478462</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.114601163669054</v>
+        <v>0.1152393933876908</v>
       </c>
       <c r="T17">
-        <v>1.001140763053006</v>
+        <v>1.010427783118433</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.31118551846814</v>
+        <v>17.16673642356388</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1028370904456603</v>
+        <v>0.1026044417726247</v>
       </c>
       <c r="C18">
-        <v>113.1429007701674</v>
+        <v>112.2954570749561</v>
       </c>
       <c r="D18">
-        <v>117.8229007701674</v>
+        <v>118.3054570749561</v>
       </c>
       <c r="E18">
-        <v>-53.62</v>
+        <v>-52.29000000000001</v>
       </c>
       <c r="F18">
-        <v>21.28</v>
+        <v>22.61</v>
       </c>
       <c r="G18">
         <v>16.6</v>
@@ -2751,28 +2751,28 @@
         <v>18.375</v>
       </c>
       <c r="M18">
-        <v>1.070384</v>
+        <v>1.137283</v>
       </c>
       <c r="N18">
-        <v>17.304616</v>
+        <v>17.237717</v>
       </c>
       <c r="O18">
-        <v>4.326154</v>
+        <v>4.30942925</v>
       </c>
       <c r="P18">
-        <v>12.978462</v>
+        <v>12.92828775</v>
       </c>
       <c r="Q18">
-        <v>17.478462</v>
+        <v>17.42828775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1152393933876908</v>
+        <v>0.1158930021356924</v>
       </c>
       <c r="T18">
-        <v>1.010427783118433</v>
+        <v>1.019938586799894</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.16673642356388</v>
+        <v>16.15692839864836</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1026044417726247</v>
+        <v>0.1023717930995891</v>
       </c>
       <c r="C19">
-        <v>112.2954570749561</v>
+        <v>111.4519823571387</v>
       </c>
       <c r="D19">
-        <v>118.3054570749561</v>
+        <v>118.7919823571387</v>
       </c>
       <c r="E19">
-        <v>-52.29000000000001</v>
+        <v>-50.96000000000001</v>
       </c>
       <c r="F19">
-        <v>22.61</v>
+        <v>23.94</v>
       </c>
       <c r="G19">
         <v>16.6</v>
@@ -2833,28 +2833,28 @@
         <v>18.375</v>
       </c>
       <c r="M19">
-        <v>1.137283</v>
+        <v>1.204182</v>
       </c>
       <c r="N19">
-        <v>17.237717</v>
+        <v>17.170818</v>
       </c>
       <c r="O19">
-        <v>4.30942925</v>
+        <v>4.2927045</v>
       </c>
       <c r="P19">
-        <v>12.92828775</v>
+        <v>12.8781135</v>
       </c>
       <c r="Q19">
-        <v>17.42828775</v>
+        <v>17.3781135</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1158930021356924</v>
+        <v>0.1165625525604746</v>
       </c>
       <c r="T19">
-        <v>1.019938586799894</v>
+        <v>1.029681361302854</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.15692839864836</v>
+        <v>15.25932126539012</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1023717930995892</v>
+        <v>0.1021391444265536</v>
       </c>
       <c r="C20">
-        <v>111.4519823571386</v>
+        <v>110.6125257855835</v>
       </c>
       <c r="D20">
-        <v>118.7919823571386</v>
+        <v>119.2825257855835</v>
       </c>
       <c r="E20">
-        <v>-50.96000000000001</v>
+        <v>-49.63000000000001</v>
       </c>
       <c r="F20">
-        <v>23.94</v>
+        <v>25.27</v>
       </c>
       <c r="G20">
         <v>16.6</v>
@@ -2915,28 +2915,28 @@
         <v>18.375</v>
       </c>
       <c r="M20">
-        <v>1.204182</v>
+        <v>1.271081</v>
       </c>
       <c r="N20">
-        <v>17.170818</v>
+        <v>17.103919</v>
       </c>
       <c r="O20">
-        <v>4.2927045</v>
+        <v>4.27597975</v>
       </c>
       <c r="P20">
-        <v>12.8781135</v>
+        <v>12.82793925</v>
       </c>
       <c r="Q20">
-        <v>17.3781135</v>
+        <v>17.32793925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1165625525604746</v>
+        <v>0.1172486350945106</v>
       </c>
       <c r="T20">
-        <v>1.029681361302854</v>
+        <v>1.039664698139221</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.25932126539012</v>
+        <v>14.45619909352748</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1021391444265536</v>
+        <v>0.101906495753518</v>
       </c>
       <c r="C21">
-        <v>110.6125257855835</v>
+        <v>109.7771373446847</v>
       </c>
       <c r="D21">
-        <v>119.2825257855835</v>
+        <v>119.7771373446847</v>
       </c>
       <c r="E21">
-        <v>-49.63000000000001</v>
+        <v>-48.3</v>
       </c>
       <c r="F21">
-        <v>25.27</v>
+        <v>26.6</v>
       </c>
       <c r="G21">
         <v>16.6</v>
@@ -2997,28 +2997,28 @@
         <v>18.375</v>
       </c>
       <c r="M21">
-        <v>1.271081</v>
+        <v>1.33798</v>
       </c>
       <c r="N21">
-        <v>17.103919</v>
+        <v>17.03702</v>
       </c>
       <c r="O21">
-        <v>4.27597975</v>
+        <v>4.259255</v>
       </c>
       <c r="P21">
-        <v>12.82793925</v>
+        <v>12.777765</v>
       </c>
       <c r="Q21">
-        <v>17.32793925</v>
+        <v>17.277765</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1172486350945106</v>
+        <v>0.1179518696918975</v>
       </c>
       <c r="T21">
-        <v>1.039664698139221</v>
+        <v>1.049897618396497</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.45619909352748</v>
+        <v>13.7333891388511</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.101906495753518</v>
+        <v>0.1016738470804824</v>
       </c>
       <c r="C22">
-        <v>109.7771373446847</v>
+        <v>108.9458678513402</v>
       </c>
       <c r="D22">
-        <v>119.7771373446847</v>
+        <v>120.2758678513402</v>
       </c>
       <c r="E22">
-        <v>-48.3</v>
+        <v>-46.97</v>
       </c>
       <c r="F22">
-        <v>26.6</v>
+        <v>27.93</v>
       </c>
       <c r="G22">
         <v>16.6</v>
@@ -3079,28 +3079,28 @@
         <v>18.375</v>
       </c>
       <c r="M22">
-        <v>1.33798</v>
+        <v>1.404879</v>
       </c>
       <c r="N22">
-        <v>17.03702</v>
+        <v>16.970121</v>
       </c>
       <c r="O22">
-        <v>4.259255</v>
+        <v>4.24253025</v>
       </c>
       <c r="P22">
-        <v>12.777765</v>
+        <v>12.72759075</v>
       </c>
       <c r="Q22">
-        <v>17.277765</v>
+        <v>17.22759075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1179518696918975</v>
+        <v>0.1186729076968132</v>
       </c>
       <c r="T22">
-        <v>1.049897618396497</v>
+        <v>1.060389599926109</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.7333891388511</v>
+        <v>13.07941822747724</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1016738470804824</v>
+        <v>0.1016886984074468</v>
       </c>
       <c r="C23">
-        <v>108.9458678513402</v>
+        <v>107.5839068951847</v>
       </c>
       <c r="D23">
-        <v>120.2758678513402</v>
+        <v>120.2439068951847</v>
       </c>
       <c r="E23">
-        <v>-46.97000000000001</v>
+        <v>-45.64</v>
       </c>
       <c r="F23">
-        <v>27.93</v>
+        <v>29.26</v>
       </c>
       <c r="G23">
         <v>16.6</v>
@@ -3161,45 +3161,45 @@
         <v>18.375</v>
       </c>
       <c r="M23">
-        <v>1.404879</v>
+        <v>1.515668</v>
       </c>
       <c r="N23">
-        <v>16.970121</v>
+        <v>16.859332</v>
       </c>
       <c r="O23">
-        <v>4.24253025</v>
+        <v>4.214833</v>
       </c>
       <c r="P23">
-        <v>12.72759075</v>
+        <v>12.644499</v>
       </c>
       <c r="Q23">
-        <v>17.22759075</v>
+        <v>17.144499</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1186729076968132</v>
+        <v>0.1194124338557011</v>
       </c>
       <c r="T23">
-        <v>1.060389599926109</v>
+        <v>1.071150606623146</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.07941822747724</v>
+        <v>12.12336738652528</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1016886984074468</v>
+        <v>0.1014672997344113</v>
       </c>
       <c r="C24">
-        <v>107.5839068951847</v>
+        <v>106.7321381288571</v>
       </c>
       <c r="D24">
-        <v>120.2439068951847</v>
+        <v>120.7221381288571</v>
       </c>
       <c r="E24">
-        <v>-45.64</v>
+        <v>-44.31</v>
       </c>
       <c r="F24">
-        <v>29.26</v>
+        <v>30.59</v>
       </c>
       <c r="G24">
         <v>16.6</v>
@@ -3243,28 +3243,28 @@
         <v>18.375</v>
       </c>
       <c r="M24">
-        <v>1.515668</v>
+        <v>1.584562</v>
       </c>
       <c r="N24">
-        <v>16.859332</v>
+        <v>16.790438</v>
       </c>
       <c r="O24">
-        <v>4.214833</v>
+        <v>4.1976095</v>
       </c>
       <c r="P24">
-        <v>12.644499</v>
+        <v>12.5928285</v>
       </c>
       <c r="Q24">
-        <v>17.144499</v>
+        <v>17.0928285</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1194124338557011</v>
+        <v>0.1201711684862484</v>
       </c>
       <c r="T24">
-        <v>1.071150606623146</v>
+        <v>1.08219111998764</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.12336738652528</v>
+        <v>11.59626445667636</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1014672997344113</v>
+        <v>0.1012459010613757</v>
       </c>
       <c r="C25">
-        <v>106.7321381288571</v>
+        <v>105.8841885721922</v>
       </c>
       <c r="D25">
-        <v>120.7221381288571</v>
+        <v>121.2041885721922</v>
       </c>
       <c r="E25">
-        <v>-44.31</v>
+        <v>-42.98</v>
       </c>
       <c r="F25">
-        <v>30.59</v>
+        <v>31.92</v>
       </c>
       <c r="G25">
         <v>16.6</v>
@@ -3325,28 +3325,28 @@
         <v>18.375</v>
       </c>
       <c r="M25">
-        <v>1.584562</v>
+        <v>1.653456</v>
       </c>
       <c r="N25">
-        <v>16.790438</v>
+        <v>16.721544</v>
       </c>
       <c r="O25">
-        <v>4.1976095</v>
+        <v>4.180386</v>
       </c>
       <c r="P25">
-        <v>12.5928285</v>
+        <v>12.541158</v>
       </c>
       <c r="Q25">
-        <v>17.0928285</v>
+        <v>17.041158</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1201711684862484</v>
+        <v>0.1209498698175996</v>
       </c>
       <c r="T25">
-        <v>1.08219111998764</v>
+        <v>1.093522173177515</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.59626445667636</v>
+        <v>11.11308677098151</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1012459010613757</v>
+        <v>0.1010245023883401</v>
       </c>
       <c r="C26">
-        <v>105.8841885721922</v>
+        <v>105.0401041595802</v>
       </c>
       <c r="D26">
-        <v>121.2041885721922</v>
+        <v>121.6901041595802</v>
       </c>
       <c r="E26">
-        <v>-42.98</v>
+        <v>-41.65000000000001</v>
       </c>
       <c r="F26">
-        <v>31.92</v>
+        <v>33.25</v>
       </c>
       <c r="G26">
         <v>16.6</v>
@@ -3407,28 +3407,28 @@
         <v>18.375</v>
       </c>
       <c r="M26">
-        <v>1.653456</v>
+        <v>1.72235</v>
       </c>
       <c r="N26">
-        <v>16.721544</v>
+        <v>16.65265</v>
       </c>
       <c r="O26">
-        <v>4.180386</v>
+        <v>4.1631625</v>
       </c>
       <c r="P26">
-        <v>12.541158</v>
+        <v>12.4894875</v>
       </c>
       <c r="Q26">
-        <v>17.041158</v>
+        <v>16.9894875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1209498698175996</v>
+        <v>0.1217493365177868</v>
       </c>
       <c r="T26">
-        <v>1.093522173177515</v>
+        <v>1.105155387785786</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.11308677098151</v>
+        <v>10.66856330014225</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1010245023883401</v>
+        <v>0.1008031037153046</v>
       </c>
       <c r="C27">
-        <v>105.0401041595802</v>
+        <v>104.1999315649925</v>
       </c>
       <c r="D27">
-        <v>121.6901041595802</v>
+        <v>122.1799315649925</v>
       </c>
       <c r="E27">
-        <v>-41.65000000000001</v>
+        <v>-40.32000000000001</v>
       </c>
       <c r="F27">
-        <v>33.25</v>
+        <v>34.58</v>
       </c>
       <c r="G27">
         <v>16.6</v>
@@ -3489,28 +3489,28 @@
         <v>18.375</v>
       </c>
       <c r="M27">
-        <v>1.72235</v>
+        <v>1.791244</v>
       </c>
       <c r="N27">
-        <v>16.65265</v>
+        <v>16.583756</v>
       </c>
       <c r="O27">
-        <v>4.1631625</v>
+        <v>4.145939</v>
       </c>
       <c r="P27">
-        <v>12.4894875</v>
+        <v>12.437817</v>
       </c>
       <c r="Q27">
-        <v>16.9894875</v>
+        <v>16.937817</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1217493365177868</v>
+        <v>0.1225704104260872</v>
       </c>
       <c r="T27">
-        <v>1.105155387785786</v>
+        <v>1.117103013599687</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.66856330014225</v>
+        <v>10.25823394244447</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1008031037153046</v>
+        <v>0.100581705042269</v>
       </c>
       <c r="C28">
-        <v>104.1999315649925</v>
+        <v>103.3637182169266</v>
       </c>
       <c r="D28">
-        <v>122.1799315649925</v>
+        <v>122.6737182169266</v>
       </c>
       <c r="E28">
-        <v>-40.32000000000001</v>
+        <v>-38.99</v>
       </c>
       <c r="F28">
-        <v>34.58</v>
+        <v>35.91</v>
       </c>
       <c r="G28">
         <v>16.6</v>
@@ -3571,28 +3571,28 @@
         <v>18.375</v>
       </c>
       <c r="M28">
-        <v>1.791244</v>
+        <v>1.860138</v>
       </c>
       <c r="N28">
-        <v>16.583756</v>
+        <v>16.514862</v>
       </c>
       <c r="O28">
-        <v>4.145939</v>
+        <v>4.1287155</v>
       </c>
       <c r="P28">
-        <v>12.437817</v>
+        <v>12.3861465</v>
       </c>
       <c r="Q28">
-        <v>16.937817</v>
+        <v>16.8861465</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1225704104260872</v>
+        <v>0.1234139795099575</v>
       </c>
       <c r="T28">
-        <v>1.117103013599687</v>
+        <v>1.129377971627666</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.25823394244447</v>
+        <v>9.878299351983562</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.100581705042269</v>
+        <v>0.1007173063692334</v>
       </c>
       <c r="C29">
-        <v>103.3637182169266</v>
+        <v>101.7308133573541</v>
       </c>
       <c r="D29">
-        <v>122.6737182169266</v>
+        <v>122.3708133573541</v>
       </c>
       <c r="E29">
-        <v>-38.99</v>
+        <v>-37.66</v>
       </c>
       <c r="F29">
-        <v>35.91</v>
+        <v>37.24</v>
       </c>
       <c r="G29">
         <v>16.6</v>
@@ -3653,45 +3653,45 @@
         <v>18.375</v>
       </c>
       <c r="M29">
-        <v>1.860138</v>
+        <v>1.99234</v>
       </c>
       <c r="N29">
-        <v>16.514862</v>
+        <v>16.38266</v>
       </c>
       <c r="O29">
-        <v>4.1287155</v>
+        <v>4.095665</v>
       </c>
       <c r="P29">
-        <v>12.3861465</v>
+        <v>12.286995</v>
       </c>
       <c r="Q29">
-        <v>16.8861465</v>
+        <v>16.786995</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1234139795099575</v>
+        <v>0.1242809810683797</v>
       </c>
       <c r="T29">
-        <v>1.129377971627666</v>
+        <v>1.141993900711979</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.878299351983562</v>
+        <v>9.222823413674373</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1007173063692334</v>
+        <v>0.1005086576961978</v>
       </c>
       <c r="C30">
-        <v>101.7308133573541</v>
+        <v>100.8675129420356</v>
       </c>
       <c r="D30">
-        <v>122.3708133573541</v>
+        <v>122.8375129420356</v>
       </c>
       <c r="E30">
-        <v>-37.66</v>
+        <v>-36.33</v>
       </c>
       <c r="F30">
-        <v>37.24</v>
+        <v>38.57000000000001</v>
       </c>
       <c r="G30">
         <v>16.6</v>
@@ -3735,28 +3735,28 @@
         <v>18.375</v>
       </c>
       <c r="M30">
-        <v>1.99234</v>
+        <v>2.063495000000001</v>
       </c>
       <c r="N30">
-        <v>16.38266</v>
+        <v>16.311505</v>
       </c>
       <c r="O30">
-        <v>4.095665</v>
+        <v>4.07787625</v>
       </c>
       <c r="P30">
-        <v>12.286995</v>
+        <v>12.23362875</v>
       </c>
       <c r="Q30">
-        <v>16.786995</v>
+        <v>16.73362875</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1242809810683797</v>
+        <v>0.1251724052059124</v>
       </c>
       <c r="T30">
-        <v>1.141993900711979</v>
+        <v>1.154965208080357</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.222823413674373</v>
+        <v>8.904795020099392</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1005086576961978</v>
+        <v>0.1003000090231622</v>
       </c>
       <c r="C31">
-        <v>100.8675129420356</v>
+        <v>100.0077859664575</v>
       </c>
       <c r="D31">
-        <v>122.8375129420356</v>
+        <v>123.3077859664575</v>
       </c>
       <c r="E31">
-        <v>-36.33000000000001</v>
+        <v>-35.00000000000001</v>
       </c>
       <c r="F31">
-        <v>38.57</v>
+        <v>39.9</v>
       </c>
       <c r="G31">
         <v>16.6</v>
@@ -3817,28 +3817,28 @@
         <v>18.375</v>
       </c>
       <c r="M31">
-        <v>2.063495</v>
+        <v>2.13465</v>
       </c>
       <c r="N31">
-        <v>16.311505</v>
+        <v>16.24035</v>
       </c>
       <c r="O31">
-        <v>4.07787625</v>
+        <v>4.0600875</v>
       </c>
       <c r="P31">
-        <v>12.23362875</v>
+        <v>12.1802625</v>
       </c>
       <c r="Q31">
-        <v>16.73362875</v>
+        <v>16.6802625</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1251724052059124</v>
+        <v>0.1260892986045175</v>
       </c>
       <c r="T31">
-        <v>1.154965208080357</v>
+        <v>1.168307124230688</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.904795020099394</v>
+        <v>8.607968519429416</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1003000090231622</v>
+        <v>0.1000913603501267</v>
       </c>
       <c r="C32">
-        <v>100.0077859664575</v>
+        <v>99.15167363018401</v>
       </c>
       <c r="D32">
-        <v>123.3077859664575</v>
+        <v>123.781673630184</v>
       </c>
       <c r="E32">
-        <v>-35.00000000000001</v>
+        <v>-33.67000000000001</v>
       </c>
       <c r="F32">
-        <v>39.9</v>
+        <v>41.23</v>
       </c>
       <c r="G32">
         <v>16.6</v>
@@ -3899,28 +3899,28 @@
         <v>18.375</v>
       </c>
       <c r="M32">
-        <v>2.13465</v>
+        <v>2.205805</v>
       </c>
       <c r="N32">
-        <v>16.24035</v>
+        <v>16.169195</v>
       </c>
       <c r="O32">
-        <v>4.0600875</v>
+        <v>4.04229875</v>
       </c>
       <c r="P32">
-        <v>12.1802625</v>
+        <v>12.12689625</v>
       </c>
       <c r="Q32">
-        <v>16.6802625</v>
+        <v>16.62689625</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1260892986045175</v>
+        <v>0.127032768623372</v>
       </c>
       <c r="T32">
-        <v>1.168307124230688</v>
+        <v>1.182035762588276</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.607968519429416</v>
+        <v>8.330292115576855</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1000913603501267</v>
+        <v>0.09988271167709112</v>
       </c>
       <c r="C33">
-        <v>99.15167363018401</v>
+        <v>98.29921776856344</v>
       </c>
       <c r="D33">
-        <v>123.781673630184</v>
+        <v>124.2592177685634</v>
       </c>
       <c r="E33">
-        <v>-33.67000000000001</v>
+        <v>-32.34</v>
       </c>
       <c r="F33">
-        <v>41.23</v>
+        <v>42.56</v>
       </c>
       <c r="G33">
         <v>16.6</v>
@@ -3981,28 +3981,28 @@
         <v>18.375</v>
       </c>
       <c r="M33">
-        <v>2.205805</v>
+        <v>2.27696</v>
       </c>
       <c r="N33">
-        <v>16.169195</v>
+        <v>16.09804</v>
       </c>
       <c r="O33">
-        <v>4.04229875</v>
+        <v>4.02451</v>
       </c>
       <c r="P33">
-        <v>12.12689625</v>
+        <v>12.07353</v>
       </c>
       <c r="Q33">
-        <v>16.62689625</v>
+        <v>16.57353</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.127032768623372</v>
+        <v>0.1280039877604281</v>
       </c>
       <c r="T33">
-        <v>1.182035762588276</v>
+        <v>1.196168184426969</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.330292115576855</v>
+        <v>8.069970486965076</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09988271167709112</v>
+        <v>0.09967406300405554</v>
       </c>
       <c r="C34">
-        <v>98.29921776856344</v>
+        <v>97.45046086504009</v>
       </c>
       <c r="D34">
-        <v>124.2592177685634</v>
+        <v>124.7404608650401</v>
       </c>
       <c r="E34">
-        <v>-32.34</v>
+        <v>-31.01000000000001</v>
       </c>
       <c r="F34">
-        <v>42.56</v>
+        <v>43.89</v>
       </c>
       <c r="G34">
         <v>16.6</v>
@@ -4063,28 +4063,28 @@
         <v>18.375</v>
       </c>
       <c r="M34">
-        <v>2.27696</v>
+        <v>2.348115</v>
       </c>
       <c r="N34">
-        <v>16.09804</v>
+        <v>16.026885</v>
       </c>
       <c r="O34">
-        <v>4.02451</v>
+        <v>4.00672125</v>
       </c>
       <c r="P34">
-        <v>12.07353</v>
+        <v>12.02016375</v>
       </c>
       <c r="Q34">
-        <v>16.57353</v>
+        <v>16.52016375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1280039877604281</v>
+        <v>0.1290041985135157</v>
       </c>
       <c r="T34">
-        <v>1.196168184426969</v>
+        <v>1.21072246960413</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.069970486965076</v>
+        <v>7.825425926754013</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09967406300405554</v>
+        <v>0.09966941433101995</v>
       </c>
       <c r="C35">
-        <v>97.45046086504009</v>
+        <v>96.13122537072613</v>
       </c>
       <c r="D35">
-        <v>124.7404608650401</v>
+        <v>124.7512253707261</v>
       </c>
       <c r="E35">
-        <v>-31.01000000000001</v>
+        <v>-29.68</v>
       </c>
       <c r="F35">
-        <v>43.89</v>
+        <v>45.22000000000001</v>
       </c>
       <c r="G35">
         <v>16.6</v>
@@ -4145,45 +4145,45 @@
         <v>18.375</v>
       </c>
       <c r="M35">
-        <v>2.348115</v>
+        <v>2.455446</v>
       </c>
       <c r="N35">
-        <v>16.026885</v>
+        <v>15.919554</v>
       </c>
       <c r="O35">
-        <v>4.00672125</v>
+        <v>3.9798885</v>
       </c>
       <c r="P35">
-        <v>12.02016375</v>
+        <v>11.9396655</v>
       </c>
       <c r="Q35">
-        <v>16.52016375</v>
+        <v>16.4396655</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1290041985135157</v>
+        <v>0.1300347186833636</v>
       </c>
       <c r="T35">
-        <v>1.21072246960413</v>
+        <v>1.225717793726054</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.825425926754013</v>
+        <v>7.48336554744026</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09966941433101995</v>
+        <v>0.09946676565798437</v>
       </c>
       <c r="C36">
-        <v>96.13122537072613</v>
+        <v>95.27229289214247</v>
       </c>
       <c r="D36">
-        <v>124.7512253707261</v>
+        <v>125.2222928921425</v>
       </c>
       <c r="E36">
-        <v>-29.68</v>
+        <v>-28.35</v>
       </c>
       <c r="F36">
-        <v>45.22000000000001</v>
+        <v>46.55</v>
       </c>
       <c r="G36">
         <v>16.6</v>
@@ -4227,28 +4227,28 @@
         <v>18.375</v>
       </c>
       <c r="M36">
-        <v>2.455446</v>
+        <v>2.527665</v>
       </c>
       <c r="N36">
-        <v>15.919554</v>
+        <v>15.847335</v>
       </c>
       <c r="O36">
-        <v>3.9798885</v>
+        <v>3.96183375</v>
       </c>
       <c r="P36">
-        <v>11.9396655</v>
+        <v>11.88550125</v>
       </c>
       <c r="Q36">
-        <v>16.4396655</v>
+        <v>16.38550125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1300347186833636</v>
+        <v>0.1310969471661298</v>
       </c>
       <c r="T36">
-        <v>1.225717793726054</v>
+        <v>1.241174512436344</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.48336554744026</v>
+        <v>7.269555103227682</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09946676565798437</v>
+        <v>0.0992641169849488</v>
       </c>
       <c r="C37">
-        <v>95.27229289214247</v>
+        <v>94.41693145198644</v>
       </c>
       <c r="D37">
-        <v>125.2222928921425</v>
+        <v>125.6969314519864</v>
       </c>
       <c r="E37">
-        <v>-28.35</v>
+        <v>-27.02</v>
       </c>
       <c r="F37">
-        <v>46.55</v>
+        <v>47.88</v>
       </c>
       <c r="G37">
         <v>16.6</v>
@@ -4309,28 +4309,28 @@
         <v>18.375</v>
       </c>
       <c r="M37">
-        <v>2.527665</v>
+        <v>2.599884</v>
       </c>
       <c r="N37">
-        <v>15.847335</v>
+        <v>15.775116</v>
       </c>
       <c r="O37">
-        <v>3.96183375</v>
+        <v>3.943779</v>
       </c>
       <c r="P37">
-        <v>11.88550125</v>
+        <v>11.831337</v>
       </c>
       <c r="Q37">
-        <v>16.38550125</v>
+        <v>16.331337</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1310969471661298</v>
+        <v>0.1321923702889825</v>
       </c>
       <c r="T37">
-        <v>1.241174512436344</v>
+        <v>1.257114253606332</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.269555103227682</v>
+        <v>7.067623017026913</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09926411698494882</v>
+        <v>0.09906146831191323</v>
       </c>
       <c r="C38">
-        <v>94.41693145198641</v>
+        <v>93.56518181140601</v>
       </c>
       <c r="D38">
-        <v>125.6969314519864</v>
+        <v>126.175181811406</v>
       </c>
       <c r="E38">
-        <v>-27.02000000000001</v>
+        <v>-25.69</v>
       </c>
       <c r="F38">
-        <v>47.88</v>
+        <v>49.21</v>
       </c>
       <c r="G38">
         <v>16.6</v>
@@ -4391,28 +4391,28 @@
         <v>18.375</v>
       </c>
       <c r="M38">
-        <v>2.599884</v>
+        <v>2.672103</v>
       </c>
       <c r="N38">
-        <v>15.775116</v>
+        <v>15.702897</v>
       </c>
       <c r="O38">
-        <v>3.943779</v>
+        <v>3.92572425</v>
       </c>
       <c r="P38">
-        <v>11.831337</v>
+        <v>11.77717275</v>
       </c>
       <c r="Q38">
-        <v>16.331337</v>
+        <v>16.27717275</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1321923702889825</v>
+        <v>0.1333225687490686</v>
       </c>
       <c r="T38">
-        <v>1.257114253606332</v>
+        <v>1.273560018305525</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.067623017026914</v>
+        <v>6.876606178728889</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09906146831191323</v>
+        <v>0.09885881963887769</v>
       </c>
       <c r="C39">
-        <v>93.56518181140601</v>
+        <v>92.71708535426896</v>
       </c>
       <c r="D39">
-        <v>126.175181811406</v>
+        <v>126.657085354269</v>
       </c>
       <c r="E39">
-        <v>-25.69</v>
+        <v>-24.36000000000001</v>
       </c>
       <c r="F39">
-        <v>49.21</v>
+        <v>50.54</v>
       </c>
       <c r="G39">
         <v>16.6</v>
@@ -4473,28 +4473,28 @@
         <v>18.375</v>
       </c>
       <c r="M39">
-        <v>2.672103</v>
+        <v>2.744322</v>
       </c>
       <c r="N39">
-        <v>15.702897</v>
+        <v>15.630678</v>
       </c>
       <c r="O39">
-        <v>3.92572425</v>
+        <v>3.9076695</v>
       </c>
       <c r="P39">
-        <v>11.77717275</v>
+        <v>11.7230085</v>
       </c>
       <c r="Q39">
-        <v>16.27717275</v>
+        <v>16.2230085</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1333225687490686</v>
+        <v>0.1344892252239963</v>
       </c>
       <c r="T39">
-        <v>1.273560018305525</v>
+        <v>1.290536291543402</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.876606178728889</v>
+        <v>6.695642858236023</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09885881963887769</v>
+        <v>0.09865617096584209</v>
       </c>
       <c r="C40">
-        <v>92.71708535426896</v>
+        <v>91.87268409910018</v>
       </c>
       <c r="D40">
-        <v>126.657085354269</v>
+        <v>127.1426840991002</v>
       </c>
       <c r="E40">
-        <v>-24.36000000000001</v>
+        <v>-23.03</v>
       </c>
       <c r="F40">
-        <v>50.54</v>
+        <v>51.87</v>
       </c>
       <c r="G40">
         <v>16.6</v>
@@ -4555,28 +4555,28 @@
         <v>18.375</v>
       </c>
       <c r="M40">
-        <v>2.744322</v>
+        <v>2.816541</v>
       </c>
       <c r="N40">
-        <v>15.630678</v>
+        <v>15.558459</v>
       </c>
       <c r="O40">
-        <v>3.9076695</v>
+        <v>3.88961475</v>
       </c>
       <c r="P40">
-        <v>11.7230085</v>
+        <v>11.66884425</v>
       </c>
       <c r="Q40">
-        <v>16.2230085</v>
+        <v>16.16884425</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1344892252239963</v>
+        <v>0.1356941327308887</v>
       </c>
       <c r="T40">
-        <v>1.290536291543402</v>
+        <v>1.308069163903832</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.695642858236023</v>
+        <v>6.523959708024842</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09865617096584209</v>
+        <v>0.09845352229280652</v>
       </c>
       <c r="C41">
-        <v>91.87268409910018</v>
+        <v>91.03202071129458</v>
       </c>
       <c r="D41">
-        <v>127.1426840991002</v>
+        <v>127.6320207112946</v>
       </c>
       <c r="E41">
-        <v>-23.03</v>
+        <v>-21.7</v>
       </c>
       <c r="F41">
-        <v>51.87</v>
+        <v>53.2</v>
       </c>
       <c r="G41">
         <v>16.6</v>
@@ -4637,28 +4637,28 @@
         <v>18.375</v>
       </c>
       <c r="M41">
-        <v>2.816541</v>
+        <v>2.88876</v>
       </c>
       <c r="N41">
-        <v>15.558459</v>
+        <v>15.48624</v>
       </c>
       <c r="O41">
-        <v>3.88961475</v>
+        <v>3.87156</v>
       </c>
       <c r="P41">
-        <v>11.66884425</v>
+        <v>11.61468</v>
       </c>
       <c r="Q41">
-        <v>16.16884425</v>
+        <v>16.11468</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1356941327308887</v>
+        <v>0.1369392038213442</v>
       </c>
       <c r="T41">
-        <v>1.308069163903832</v>
+        <v>1.326186465342943</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.523959708024842</v>
+        <v>6.360860715324223</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09845352229280652</v>
+        <v>0.09825087361977095</v>
       </c>
       <c r="C42">
-        <v>91.03202071129458</v>
+        <v>90.19513851561354</v>
       </c>
       <c r="D42">
-        <v>127.6320207112946</v>
+        <v>128.1251385156135</v>
       </c>
       <c r="E42">
-        <v>-21.7</v>
+        <v>-20.37</v>
       </c>
       <c r="F42">
-        <v>53.2</v>
+        <v>54.53</v>
       </c>
       <c r="G42">
         <v>16.6</v>
@@ -4719,28 +4719,28 @@
         <v>18.375</v>
       </c>
       <c r="M42">
-        <v>2.88876</v>
+        <v>2.960979</v>
       </c>
       <c r="N42">
-        <v>15.48624</v>
+        <v>15.414021</v>
       </c>
       <c r="O42">
-        <v>3.87156</v>
+        <v>3.85350525</v>
       </c>
       <c r="P42">
-        <v>11.61468</v>
+        <v>11.56051575</v>
       </c>
       <c r="Q42">
-        <v>16.11468</v>
+        <v>16.06051575</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1369392038213442</v>
+        <v>0.1382264807114762</v>
       </c>
       <c r="T42">
-        <v>1.326186465342943</v>
+        <v>1.34491791259355</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.360860715324223</v>
+        <v>6.205717771048022</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09825087361977095</v>
+        <v>0.09836322494673538</v>
       </c>
       <c r="C43">
-        <v>90.19513851561354</v>
+        <v>88.59127728764818</v>
       </c>
       <c r="D43">
-        <v>128.1251385156135</v>
+        <v>127.8512772876482</v>
       </c>
       <c r="E43">
-        <v>-20.37</v>
+        <v>-19.04</v>
       </c>
       <c r="F43">
-        <v>54.53</v>
+        <v>55.86000000000001</v>
       </c>
       <c r="G43">
         <v>16.6</v>
@@ -4801,45 +4801,45 @@
         <v>18.375</v>
       </c>
       <c r="M43">
-        <v>2.960979</v>
+        <v>3.089058000000001</v>
       </c>
       <c r="N43">
-        <v>15.414021</v>
+        <v>15.285942</v>
       </c>
       <c r="O43">
-        <v>3.85350525</v>
+        <v>3.8214855</v>
       </c>
       <c r="P43">
-        <v>11.56051575</v>
+        <v>11.4644565</v>
       </c>
       <c r="Q43">
-        <v>16.06051575</v>
+        <v>15.9644565</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1382264807114762</v>
+        <v>0.1395581464598886</v>
       </c>
       <c r="T43">
-        <v>1.34491791259355</v>
+        <v>1.364295271818315</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.205717771048022</v>
+        <v>5.948415342152849</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09836322494673538</v>
+        <v>0.09816807627369981</v>
       </c>
       <c r="C44">
-        <v>88.5912772876482</v>
+        <v>87.73771272091079</v>
       </c>
       <c r="D44">
-        <v>127.8512772876482</v>
+        <v>128.3277127209108</v>
       </c>
       <c r="E44">
-        <v>-19.04000000000001</v>
+        <v>-17.71000000000001</v>
       </c>
       <c r="F44">
-        <v>55.86</v>
+        <v>57.19</v>
       </c>
       <c r="G44">
         <v>16.6</v>
@@ -4883,28 +4883,28 @@
         <v>18.375</v>
       </c>
       <c r="M44">
-        <v>3.089058</v>
+        <v>3.162607</v>
       </c>
       <c r="N44">
-        <v>15.285942</v>
+        <v>15.212393</v>
       </c>
       <c r="O44">
-        <v>3.8214855</v>
+        <v>3.80309825</v>
       </c>
       <c r="P44">
-        <v>11.4644565</v>
+        <v>11.40929475</v>
       </c>
       <c r="Q44">
-        <v>15.9644565</v>
+        <v>15.90929475</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1395581464598886</v>
+        <v>0.1409365373222803</v>
       </c>
       <c r="T44">
-        <v>1.364295271818315</v>
+        <v>1.384352538384301</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.948415342152851</v>
+        <v>5.810080101637668</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09816807627369981</v>
+        <v>0.09797292760066424</v>
       </c>
       <c r="C45">
-        <v>87.73771272091079</v>
+        <v>86.88771229162407</v>
       </c>
       <c r="D45">
-        <v>128.3277127209108</v>
+        <v>128.8077122916241</v>
       </c>
       <c r="E45">
-        <v>-17.71000000000001</v>
+        <v>-16.38</v>
       </c>
       <c r="F45">
-        <v>57.19</v>
+        <v>58.52</v>
       </c>
       <c r="G45">
         <v>16.6</v>
@@ -4965,28 +4965,28 @@
         <v>18.375</v>
       </c>
       <c r="M45">
-        <v>3.162607</v>
+        <v>3.236156</v>
       </c>
       <c r="N45">
-        <v>15.212393</v>
+        <v>15.138844</v>
       </c>
       <c r="O45">
-        <v>3.80309825</v>
+        <v>3.784711</v>
       </c>
       <c r="P45">
-        <v>11.40929475</v>
+        <v>11.354133</v>
       </c>
       <c r="Q45">
-        <v>15.90929475</v>
+        <v>15.854133</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1409365373222803</v>
+        <v>0.1423641564297576</v>
       </c>
       <c r="T45">
-        <v>1.384352538384301</v>
+        <v>1.405126135899071</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.810080101637668</v>
+        <v>5.678032826600448</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09797292760066424</v>
+        <v>0.09777777892762868</v>
       </c>
       <c r="C46">
-        <v>86.88771229162407</v>
+        <v>86.04131614405986</v>
       </c>
       <c r="D46">
-        <v>128.8077122916241</v>
+        <v>129.2913161440599</v>
       </c>
       <c r="E46">
-        <v>-16.38</v>
+        <v>-15.05</v>
       </c>
       <c r="F46">
-        <v>58.52</v>
+        <v>59.85</v>
       </c>
       <c r="G46">
         <v>16.6</v>
@@ -5047,28 +5047,28 @@
         <v>18.375</v>
       </c>
       <c r="M46">
-        <v>3.236156</v>
+        <v>3.309705</v>
       </c>
       <c r="N46">
-        <v>15.138844</v>
+        <v>15.065295</v>
       </c>
       <c r="O46">
-        <v>3.784711</v>
+        <v>3.76632375</v>
       </c>
       <c r="P46">
-        <v>11.354133</v>
+        <v>11.29897125</v>
       </c>
       <c r="Q46">
-        <v>15.854133</v>
+        <v>15.79897125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1423641564297576</v>
+        <v>0.1438436889593248</v>
       </c>
       <c r="T46">
-        <v>1.405126135899071</v>
+        <v>1.426655136959833</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.678032826600448</v>
+        <v>5.55185431934266</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09777777892762868</v>
+        <v>0.09758263025459307</v>
       </c>
       <c r="C47">
-        <v>86.04131614405986</v>
+        <v>85.19856502764284</v>
       </c>
       <c r="D47">
-        <v>129.2913161440599</v>
+        <v>129.7785650276429</v>
       </c>
       <c r="E47">
-        <v>-15.05</v>
+        <v>-13.72000000000001</v>
       </c>
       <c r="F47">
-        <v>59.85</v>
+        <v>61.18</v>
       </c>
       <c r="G47">
         <v>16.6</v>
@@ -5129,28 +5129,28 @@
         <v>18.375</v>
       </c>
       <c r="M47">
-        <v>3.309705</v>
+        <v>3.383254</v>
       </c>
       <c r="N47">
-        <v>15.065295</v>
+        <v>14.991746</v>
       </c>
       <c r="O47">
-        <v>3.76632375</v>
+        <v>3.7479365</v>
       </c>
       <c r="P47">
-        <v>11.29897125</v>
+        <v>11.2438095</v>
       </c>
       <c r="Q47">
-        <v>15.79897125</v>
+        <v>15.7438095</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1438436889593248</v>
+        <v>0.1453780189899872</v>
       </c>
       <c r="T47">
-        <v>1.426655136959833</v>
+        <v>1.448981508430253</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.55185431934266</v>
+        <v>5.431161834139559</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09758263025459307</v>
+        <v>0.09738748158155751</v>
       </c>
       <c r="C48">
-        <v>85.19856502764284</v>
+        <v>84.35950030839628</v>
       </c>
       <c r="D48">
-        <v>129.7785650276429</v>
+        <v>130.2695003083963</v>
       </c>
       <c r="E48">
-        <v>-13.72000000000001</v>
+        <v>-12.39</v>
       </c>
       <c r="F48">
-        <v>61.18</v>
+        <v>62.51000000000001</v>
       </c>
       <c r="G48">
         <v>16.6</v>
@@ -5211,28 +5211,28 @@
         <v>18.375</v>
       </c>
       <c r="M48">
-        <v>3.383254</v>
+        <v>3.456803</v>
       </c>
       <c r="N48">
-        <v>14.991746</v>
+        <v>14.918197</v>
       </c>
       <c r="O48">
-        <v>3.7479365</v>
+        <v>3.72954925</v>
       </c>
       <c r="P48">
-        <v>11.2438095</v>
+        <v>11.18864775</v>
       </c>
       <c r="Q48">
-        <v>15.7438095</v>
+        <v>15.68864775</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1453780189899872</v>
+        <v>0.1469702482670896</v>
       </c>
       <c r="T48">
-        <v>1.448981508430253</v>
+        <v>1.472150384484462</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.431161834139559</v>
+        <v>5.315605199370632</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09738748158155751</v>
+        <v>0.09719233290852194</v>
       </c>
       <c r="C49">
-        <v>84.35950030839628</v>
+        <v>83.52416398064949</v>
       </c>
       <c r="D49">
-        <v>130.2695003083963</v>
+        <v>130.7641639806495</v>
       </c>
       <c r="E49">
-        <v>-12.39</v>
+        <v>-11.06</v>
       </c>
       <c r="F49">
-        <v>62.51000000000001</v>
+        <v>63.84</v>
       </c>
       <c r="G49">
         <v>16.6</v>
@@ -5293,28 +5293,28 @@
         <v>18.375</v>
       </c>
       <c r="M49">
-        <v>3.456803</v>
+        <v>3.530352</v>
       </c>
       <c r="N49">
-        <v>14.918197</v>
+        <v>14.844648</v>
       </c>
       <c r="O49">
-        <v>3.72954925</v>
+        <v>3.711162</v>
       </c>
       <c r="P49">
-        <v>11.18864775</v>
+        <v>11.133486</v>
       </c>
       <c r="Q49">
-        <v>15.68864775</v>
+        <v>15.633486</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1469702482670896</v>
+        <v>0.1486237171317729</v>
       </c>
       <c r="T49">
-        <v>1.472150384484462</v>
+        <v>1.496210371156141</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.315605199370632</v>
+        <v>5.204863424383744</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09719233290852193</v>
+        <v>0.09699718423548637</v>
       </c>
       <c r="C50">
-        <v>83.52416398064952</v>
+        <v>82.69259867901211</v>
       </c>
       <c r="D50">
-        <v>130.7641639806495</v>
+        <v>131.2625986790121</v>
       </c>
       <c r="E50">
-        <v>-11.06000000000001</v>
+        <v>-9.730000000000004</v>
       </c>
       <c r="F50">
-        <v>63.84</v>
+        <v>65.17</v>
       </c>
       <c r="G50">
         <v>16.6</v>
@@ -5375,28 +5375,28 @@
         <v>18.375</v>
       </c>
       <c r="M50">
-        <v>3.530352</v>
+        <v>3.603901</v>
       </c>
       <c r="N50">
-        <v>14.844648</v>
+        <v>14.771099</v>
       </c>
       <c r="O50">
-        <v>3.711162</v>
+        <v>3.69277475</v>
       </c>
       <c r="P50">
-        <v>11.133486</v>
+        <v>11.07832425</v>
       </c>
       <c r="Q50">
-        <v>15.633486</v>
+        <v>15.57832425</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1486237171317729</v>
+        <v>0.1503420279127184</v>
       </c>
       <c r="T50">
-        <v>1.496210371156141</v>
+        <v>1.521213886716906</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.204863424383745</v>
+        <v>5.098641721845301</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09699718423548637</v>
+        <v>0.09680203556245079</v>
       </c>
       <c r="C51">
-        <v>82.69259867901211</v>
+        <v>81.86484769062352</v>
       </c>
       <c r="D51">
-        <v>131.2625986790121</v>
+        <v>131.7648476906235</v>
       </c>
       <c r="E51">
-        <v>-9.730000000000004</v>
+        <v>-8.400000000000006</v>
       </c>
       <c r="F51">
-        <v>65.17</v>
+        <v>66.5</v>
       </c>
       <c r="G51">
         <v>16.6</v>
@@ -5457,28 +5457,28 @@
         <v>18.375</v>
       </c>
       <c r="M51">
-        <v>3.603901</v>
+        <v>3.67745</v>
       </c>
       <c r="N51">
-        <v>14.771099</v>
+        <v>14.69755</v>
       </c>
       <c r="O51">
-        <v>3.69277475</v>
+        <v>3.6743875</v>
       </c>
       <c r="P51">
-        <v>11.07832425</v>
+        <v>11.0231625</v>
       </c>
       <c r="Q51">
-        <v>15.57832425</v>
+        <v>15.5231625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1503420279127184</v>
+        <v>0.1521290711249016</v>
       </c>
       <c r="T51">
-        <v>1.521213886716906</v>
+        <v>1.547217542900101</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.098641721845301</v>
+        <v>4.996668887408394</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09680203556245079</v>
+        <v>0.09660688688941521</v>
       </c>
       <c r="C52">
-        <v>81.86484769062352</v>
+        <v>81.04095496768475</v>
       </c>
       <c r="D52">
-        <v>131.7648476906235</v>
+        <v>132.2709549676848</v>
       </c>
       <c r="E52">
-        <v>-8.400000000000006</v>
+        <v>-7.070000000000007</v>
       </c>
       <c r="F52">
-        <v>66.5</v>
+        <v>67.83</v>
       </c>
       <c r="G52">
         <v>16.6</v>
@@ -5539,28 +5539,28 @@
         <v>18.375</v>
       </c>
       <c r="M52">
-        <v>3.67745</v>
+        <v>3.750999</v>
       </c>
       <c r="N52">
-        <v>14.69755</v>
+        <v>14.624001</v>
       </c>
       <c r="O52">
-        <v>3.6743875</v>
+        <v>3.65600025</v>
       </c>
       <c r="P52">
-        <v>11.0231625</v>
+        <v>10.96800075</v>
       </c>
       <c r="Q52">
-        <v>15.5231625</v>
+        <v>15.46800075</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1521290711249016</v>
+        <v>0.1539890548763576</v>
       </c>
       <c r="T52">
-        <v>1.547217542900101</v>
+        <v>1.574282572805059</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.996668887408394</v>
+        <v>4.898694987655288</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09660688688941521</v>
+        <v>0.09641173821637965</v>
       </c>
       <c r="C53">
-        <v>81.04095496768475</v>
+        <v>80.22096514028019</v>
       </c>
       <c r="D53">
-        <v>132.2709549676848</v>
+        <v>132.7809651402802</v>
       </c>
       <c r="E53">
-        <v>-7.070000000000007</v>
+        <v>-5.740000000000009</v>
       </c>
       <c r="F53">
-        <v>67.83</v>
+        <v>69.16</v>
       </c>
       <c r="G53">
         <v>16.6</v>
@@ -5621,28 +5621,28 @@
         <v>18.375</v>
       </c>
       <c r="M53">
-        <v>3.750999</v>
+        <v>3.824548</v>
       </c>
       <c r="N53">
-        <v>14.624001</v>
+        <v>14.550452</v>
       </c>
       <c r="O53">
-        <v>3.65600025</v>
+        <v>3.637613</v>
       </c>
       <c r="P53">
-        <v>10.96800075</v>
+        <v>10.912839</v>
       </c>
       <c r="Q53">
-        <v>15.46800075</v>
+        <v>15.412839</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1539890548763576</v>
+        <v>0.1559265379507909</v>
       </c>
       <c r="T53">
-        <v>1.574282572805059</v>
+        <v>1.60247531228939</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.898694987655288</v>
+        <v>4.804489314815764</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09641173821637965</v>
+        <v>0.09621658954334406</v>
       </c>
       <c r="C54">
-        <v>80.22096514028019</v>
+        <v>79.40492352949718</v>
       </c>
       <c r="D54">
-        <v>132.7809651402802</v>
+        <v>133.2949235294972</v>
       </c>
       <c r="E54">
-        <v>-5.740000000000009</v>
+        <v>-4.409999999999997</v>
       </c>
       <c r="F54">
-        <v>69.16</v>
+        <v>70.49000000000001</v>
       </c>
       <c r="G54">
         <v>16.6</v>
@@ -5703,28 +5703,28 @@
         <v>18.375</v>
       </c>
       <c r="M54">
-        <v>3.824548</v>
+        <v>3.898097000000001</v>
       </c>
       <c r="N54">
-        <v>14.550452</v>
+        <v>14.476903</v>
       </c>
       <c r="O54">
-        <v>3.637613</v>
+        <v>3.61922575</v>
       </c>
       <c r="P54">
-        <v>10.912839</v>
+        <v>10.85767725</v>
       </c>
       <c r="Q54">
-        <v>15.412839</v>
+        <v>15.35767725</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1559265379507909</v>
+        <v>0.157946467113498</v>
       </c>
       <c r="T54">
-        <v>1.60247531228939</v>
+        <v>1.631867742815608</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.804489314815764</v>
+        <v>4.713838573026786</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09621658954334406</v>
+        <v>0.09602144087030849</v>
       </c>
       <c r="C55">
-        <v>79.40492352949718</v>
+        <v>78.59287616085102</v>
       </c>
       <c r="D55">
-        <v>133.2949235294972</v>
+        <v>133.812876160851</v>
       </c>
       <c r="E55">
-        <v>-4.409999999999997</v>
+        <v>-3.079999999999998</v>
       </c>
       <c r="F55">
-        <v>70.49000000000001</v>
+        <v>71.82000000000001</v>
       </c>
       <c r="G55">
         <v>16.6</v>
@@ -5785,28 +5785,28 @@
         <v>18.375</v>
       </c>
       <c r="M55">
-        <v>3.898097000000001</v>
+        <v>3.971646000000001</v>
       </c>
       <c r="N55">
-        <v>14.476903</v>
+        <v>14.403354</v>
       </c>
       <c r="O55">
-        <v>3.61922575</v>
+        <v>3.6008385</v>
       </c>
       <c r="P55">
-        <v>10.85767725</v>
+        <v>10.8025155</v>
       </c>
       <c r="Q55">
-        <v>15.35767725</v>
+        <v>15.3025155</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.157946467113498</v>
+        <v>0.1600542192832793</v>
       </c>
       <c r="T55">
-        <v>1.631867742815608</v>
+        <v>1.662538105103835</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.713838573026786</v>
+        <v>4.626545266118884</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09602144087030849</v>
+        <v>0.09582629219727291</v>
       </c>
       <c r="C56">
-        <v>78.59287616085102</v>
+        <v>77.78486977802515</v>
       </c>
       <c r="D56">
-        <v>133.812876160851</v>
+        <v>134.3348697780252</v>
       </c>
       <c r="E56">
-        <v>-3.079999999999998</v>
+        <v>-1.75</v>
       </c>
       <c r="F56">
-        <v>71.82000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="G56">
         <v>16.6</v>
@@ -5867,28 +5867,28 @@
         <v>18.375</v>
       </c>
       <c r="M56">
-        <v>3.971646000000001</v>
+        <v>4.045195000000001</v>
       </c>
       <c r="N56">
-        <v>14.403354</v>
+        <v>14.329805</v>
       </c>
       <c r="O56">
-        <v>3.6008385</v>
+        <v>3.58245125</v>
       </c>
       <c r="P56">
-        <v>10.8025155</v>
+        <v>10.74735375</v>
       </c>
       <c r="Q56">
-        <v>15.3025155</v>
+        <v>15.24735375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1600542192832793</v>
+        <v>0.1622556493272732</v>
       </c>
       <c r="T56">
-        <v>1.662538105103835</v>
+        <v>1.694571594604872</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.626545266118884</v>
+        <v>4.542426261280358</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09582629219727291</v>
+        <v>0.09668114352423733</v>
       </c>
       <c r="C57">
-        <v>77.78486977802515</v>
+        <v>74.19791693197455</v>
       </c>
       <c r="D57">
-        <v>134.3348697780252</v>
+        <v>132.0779169319746</v>
       </c>
       <c r="E57">
-        <v>-1.75</v>
+        <v>-0.4200000000000017</v>
       </c>
       <c r="F57">
-        <v>73.15000000000001</v>
+        <v>74.48</v>
       </c>
       <c r="G57">
         <v>16.6</v>
@@ -5949,45 +5949,45 @@
         <v>18.375</v>
       </c>
       <c r="M57">
-        <v>4.045195000000001</v>
+        <v>4.304944000000001</v>
       </c>
       <c r="N57">
-        <v>14.329805</v>
+        <v>14.070056</v>
       </c>
       <c r="O57">
-        <v>3.58245125</v>
+        <v>3.517514</v>
       </c>
       <c r="P57">
-        <v>10.74735375</v>
+        <v>10.552542</v>
       </c>
       <c r="Q57">
-        <v>15.24735375</v>
+        <v>15.052542</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1622556493272732</v>
+        <v>0.1645571443732667</v>
       </c>
       <c r="T57">
-        <v>1.694571594604872</v>
+        <v>1.728061151810502</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.542426261280358</v>
+        <v>4.268348206155526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09668114352423733</v>
+        <v>0.09650474485120178</v>
       </c>
       <c r="C58">
-        <v>74.19791693197455</v>
+        <v>73.32740784061576</v>
       </c>
       <c r="D58">
-        <v>132.0779169319746</v>
+        <v>132.5374078406158</v>
       </c>
       <c r="E58">
-        <v>-0.4200000000000017</v>
+        <v>0.9099999999999966</v>
       </c>
       <c r="F58">
-        <v>74.48</v>
+        <v>75.81</v>
       </c>
       <c r="G58">
         <v>16.6</v>
@@ -6031,28 +6031,28 @@
         <v>18.375</v>
       </c>
       <c r="M58">
-        <v>4.304944000000001</v>
+        <v>4.381818000000001</v>
       </c>
       <c r="N58">
-        <v>14.070056</v>
+        <v>13.993182</v>
       </c>
       <c r="O58">
-        <v>3.517514</v>
+        <v>3.4982955</v>
       </c>
       <c r="P58">
-        <v>10.552542</v>
+        <v>10.4948865</v>
       </c>
       <c r="Q58">
-        <v>15.052542</v>
+        <v>14.9948865</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1645571443732667</v>
+        <v>0.1669656857004692</v>
       </c>
       <c r="T58">
-        <v>1.728061151810502</v>
+        <v>1.76310836283965</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.268348206155526</v>
+        <v>4.193464904293149</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09650474485120178</v>
+        <v>0.0963283461781662</v>
       </c>
       <c r="C59">
-        <v>73.32740784061576</v>
+        <v>72.46010699146908</v>
       </c>
       <c r="D59">
-        <v>132.5374078406158</v>
+        <v>133.0001069914691</v>
       </c>
       <c r="E59">
-        <v>0.9099999999999966</v>
+        <v>2.240000000000009</v>
       </c>
       <c r="F59">
-        <v>75.81</v>
+        <v>77.14000000000001</v>
       </c>
       <c r="G59">
         <v>16.6</v>
@@ -6113,28 +6113,28 @@
         <v>18.375</v>
       </c>
       <c r="M59">
-        <v>4.381818000000001</v>
+        <v>4.458692000000001</v>
       </c>
       <c r="N59">
-        <v>13.993182</v>
+        <v>13.916308</v>
       </c>
       <c r="O59">
-        <v>3.4982955</v>
+        <v>3.479077</v>
       </c>
       <c r="P59">
-        <v>10.4948865</v>
+        <v>10.437231</v>
       </c>
       <c r="Q59">
-        <v>14.9948865</v>
+        <v>14.937231</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1669656857004692</v>
+        <v>0.1694889194718243</v>
       </c>
       <c r="T59">
-        <v>1.76310836283965</v>
+        <v>1.799824488679709</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.193464904293149</v>
+        <v>4.121163785253612</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0963283461781662</v>
+        <v>0.09615194750513063</v>
       </c>
       <c r="C60">
-        <v>72.46010699146909</v>
+        <v>71.59604810297213</v>
       </c>
       <c r="D60">
-        <v>133.0001069914691</v>
+        <v>133.4660481029721</v>
       </c>
       <c r="E60">
-        <v>2.239999999999995</v>
+        <v>3.569999999999993</v>
       </c>
       <c r="F60">
-        <v>77.14</v>
+        <v>78.47</v>
       </c>
       <c r="G60">
         <v>16.6</v>
@@ -6195,28 +6195,28 @@
         <v>18.375</v>
       </c>
       <c r="M60">
-        <v>4.458692</v>
+        <v>4.535566</v>
       </c>
       <c r="N60">
-        <v>13.916308</v>
+        <v>13.839434</v>
       </c>
       <c r="O60">
-        <v>3.479077</v>
+        <v>3.4598585</v>
       </c>
       <c r="P60">
-        <v>10.437231</v>
+        <v>10.3795755</v>
       </c>
       <c r="Q60">
-        <v>14.937231</v>
+        <v>14.8795755</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1694889194718243</v>
+        <v>0.1721352378173918</v>
       </c>
       <c r="T60">
-        <v>1.799824488679709</v>
+        <v>1.838331645048551</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.121163785253612</v>
+        <v>4.051313551605246</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09615194750513063</v>
+        <v>0.09755054883209505</v>
       </c>
       <c r="C61">
-        <v>71.59604810297213</v>
+        <v>66.65901791306725</v>
       </c>
       <c r="D61">
-        <v>133.4660481029721</v>
+        <v>129.8590179130672</v>
       </c>
       <c r="E61">
-        <v>3.569999999999993</v>
+        <v>4.899999999999991</v>
       </c>
       <c r="F61">
-        <v>78.47</v>
+        <v>79.8</v>
       </c>
       <c r="G61">
         <v>16.6</v>
@@ -6277,45 +6277,45 @@
         <v>18.375</v>
       </c>
       <c r="M61">
-        <v>4.535566</v>
+        <v>4.89174</v>
       </c>
       <c r="N61">
-        <v>13.839434</v>
+        <v>13.48326</v>
       </c>
       <c r="O61">
-        <v>3.4598585</v>
+        <v>3.370815</v>
       </c>
       <c r="P61">
-        <v>10.3795755</v>
+        <v>10.112445</v>
       </c>
       <c r="Q61">
-        <v>14.8795755</v>
+        <v>14.612445</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1721352378173918</v>
+        <v>0.1749138720802376</v>
       </c>
       <c r="T61">
-        <v>1.838331645048551</v>
+        <v>1.878764159235836</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.051313551605246</v>
+        <v>3.756332102687388</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09755054883209505</v>
+        <v>0.09740040015905949</v>
       </c>
       <c r="C62">
-        <v>66.65901791306725</v>
+        <v>65.70688628542959</v>
       </c>
       <c r="D62">
-        <v>129.8590179130672</v>
+        <v>130.2368862854296</v>
       </c>
       <c r="E62">
-        <v>4.899999999999991</v>
+        <v>6.22999999999999</v>
       </c>
       <c r="F62">
-        <v>79.8</v>
+        <v>81.13</v>
       </c>
       <c r="G62">
         <v>16.6</v>
@@ -6359,28 +6359,28 @@
         <v>18.375</v>
       </c>
       <c r="M62">
-        <v>4.89174</v>
+        <v>4.973269</v>
       </c>
       <c r="N62">
-        <v>13.48326</v>
+        <v>13.401731</v>
       </c>
       <c r="O62">
-        <v>3.370815</v>
+        <v>3.35043275</v>
       </c>
       <c r="P62">
-        <v>10.112445</v>
+        <v>10.05129825</v>
       </c>
       <c r="Q62">
-        <v>14.612445</v>
+        <v>14.55129825</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1749138720802376</v>
+        <v>0.1778350004078448</v>
       </c>
       <c r="T62">
-        <v>1.878764159235836</v>
+        <v>1.921270135689136</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.756332102687388</v>
+        <v>3.694752887889234</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09740040015905949</v>
+        <v>0.09725025148602391</v>
       </c>
       <c r="C63">
-        <v>65.70688628542959</v>
+        <v>64.75696014495882</v>
       </c>
       <c r="D63">
-        <v>130.2368862854296</v>
+        <v>130.6169601449588</v>
       </c>
       <c r="E63">
-        <v>6.22999999999999</v>
+        <v>7.559999999999988</v>
       </c>
       <c r="F63">
-        <v>81.13</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="G63">
         <v>16.6</v>
@@ -6441,28 +6441,28 @@
         <v>18.375</v>
       </c>
       <c r="M63">
-        <v>4.973269</v>
+        <v>5.054798</v>
       </c>
       <c r="N63">
-        <v>13.401731</v>
+        <v>13.320202</v>
       </c>
       <c r="O63">
-        <v>3.35043275</v>
+        <v>3.3300505</v>
       </c>
       <c r="P63">
-        <v>10.05129825</v>
+        <v>9.9901515</v>
       </c>
       <c r="Q63">
-        <v>14.55129825</v>
+        <v>14.4901515</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1778350004078448</v>
+        <v>0.1809098723316419</v>
       </c>
       <c r="T63">
-        <v>1.921270135689136</v>
+        <v>1.966013268797872</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.694752887889234</v>
+        <v>3.635160099374891</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09725025148602391</v>
+        <v>0.09710010281298834</v>
       </c>
       <c r="C64">
-        <v>64.75696014495882</v>
+        <v>63.80925885716995</v>
       </c>
       <c r="D64">
-        <v>130.6169601449588</v>
+        <v>130.99925885717</v>
       </c>
       <c r="E64">
-        <v>7.559999999999988</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F64">
-        <v>82.45999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="G64">
         <v>16.6</v>
@@ -6523,28 +6523,28 @@
         <v>18.375</v>
       </c>
       <c r="M64">
-        <v>5.054798</v>
+        <v>5.136327000000001</v>
       </c>
       <c r="N64">
-        <v>13.320202</v>
+        <v>13.238673</v>
       </c>
       <c r="O64">
-        <v>3.3300505</v>
+        <v>3.30966825</v>
       </c>
       <c r="P64">
-        <v>9.9901515</v>
+        <v>9.929004749999999</v>
       </c>
       <c r="Q64">
-        <v>14.4901515</v>
+        <v>14.42900475</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1809098723316419</v>
+        <v>0.1841509535486171</v>
       </c>
       <c r="T64">
-        <v>1.966013268797872</v>
+        <v>2.013174949642216</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.635160099374891</v>
+        <v>3.577459145416559</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09710010281298834</v>
+        <v>0.09694995413995276</v>
       </c>
       <c r="C65">
-        <v>63.80925885716995</v>
+        <v>62.86380201496499</v>
       </c>
       <c r="D65">
-        <v>130.99925885717</v>
+        <v>131.383802014965</v>
       </c>
       <c r="E65">
-        <v>8.890000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="F65">
-        <v>83.79000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="G65">
         <v>16.6</v>
@@ -6605,28 +6605,28 @@
         <v>18.375</v>
       </c>
       <c r="M65">
-        <v>5.136327000000001</v>
+        <v>5.217856</v>
       </c>
       <c r="N65">
-        <v>13.238673</v>
+        <v>13.157144</v>
       </c>
       <c r="O65">
-        <v>3.30966825</v>
+        <v>3.289286</v>
       </c>
       <c r="P65">
-        <v>9.929004749999999</v>
+        <v>9.867857999999998</v>
       </c>
       <c r="Q65">
-        <v>14.42900475</v>
+        <v>14.367858</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1841509535486171</v>
+        <v>0.1875720948332021</v>
       </c>
       <c r="T65">
-        <v>2.013174949642216</v>
+        <v>2.062956723866801</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.577459145416559</v>
+        <v>3.521561346269425</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09694995413995276</v>
+        <v>0.09816480546691719</v>
       </c>
       <c r="C66">
-        <v>62.86380201496499</v>
+        <v>58.48572831744401</v>
       </c>
       <c r="D66">
-        <v>131.383802014965</v>
+        <v>128.335728317444</v>
       </c>
       <c r="E66">
-        <v>10.22</v>
+        <v>11.55</v>
       </c>
       <c r="F66">
-        <v>85.12</v>
+        <v>86.45</v>
       </c>
       <c r="G66">
         <v>16.6</v>
@@ -6687,45 +6687,45 @@
         <v>18.375</v>
       </c>
       <c r="M66">
-        <v>5.217856</v>
+        <v>5.541445</v>
       </c>
       <c r="N66">
-        <v>13.157144</v>
+        <v>12.833555</v>
       </c>
       <c r="O66">
-        <v>3.289286</v>
+        <v>3.20838875</v>
       </c>
       <c r="P66">
-        <v>9.867857999999998</v>
+        <v>9.625166249999999</v>
       </c>
       <c r="Q66">
-        <v>14.367858</v>
+        <v>14.12516625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1875720948332021</v>
+        <v>0.1911887299054777</v>
       </c>
       <c r="T66">
-        <v>2.062956723866801</v>
+        <v>2.11558317090422</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.521561346269425</v>
+        <v>3.315922110568633</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09816480546691719</v>
+        <v>0.09803565679388161</v>
       </c>
       <c r="C67">
-        <v>58.48572831744401</v>
+        <v>57.47302860679721</v>
       </c>
       <c r="D67">
-        <v>128.335728317444</v>
+        <v>128.6530286067972</v>
       </c>
       <c r="E67">
-        <v>11.55</v>
+        <v>12.88</v>
       </c>
       <c r="F67">
-        <v>86.45</v>
+        <v>87.78</v>
       </c>
       <c r="G67">
         <v>16.6</v>
@@ -6769,28 +6769,28 @@
         <v>18.375</v>
       </c>
       <c r="M67">
-        <v>5.541445</v>
+        <v>5.626698</v>
       </c>
       <c r="N67">
-        <v>12.833555</v>
+        <v>12.748302</v>
       </c>
       <c r="O67">
-        <v>3.20838875</v>
+        <v>3.1870755</v>
       </c>
       <c r="P67">
-        <v>9.625166249999999</v>
+        <v>9.5612265</v>
       </c>
       <c r="Q67">
-        <v>14.12516625</v>
+        <v>14.0612265</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1911887299054777</v>
+        <v>0.1950181082172989</v>
       </c>
       <c r="T67">
-        <v>2.11558317090422</v>
+        <v>2.17130529129678</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.315922110568633</v>
+        <v>3.265680866469108</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09803565679388161</v>
+        <v>0.09790650812084604</v>
       </c>
       <c r="C68">
-        <v>57.47302860679721</v>
+        <v>56.46190178647835</v>
       </c>
       <c r="D68">
-        <v>128.6530286067972</v>
+        <v>128.9719017864784</v>
       </c>
       <c r="E68">
-        <v>12.88</v>
+        <v>14.20999999999999</v>
       </c>
       <c r="F68">
-        <v>87.78</v>
+        <v>89.11</v>
       </c>
       <c r="G68">
         <v>16.6</v>
@@ -6851,28 +6851,28 @@
         <v>18.375</v>
       </c>
       <c r="M68">
-        <v>5.626698</v>
+        <v>5.711951</v>
       </c>
       <c r="N68">
-        <v>12.748302</v>
+        <v>12.663049</v>
       </c>
       <c r="O68">
-        <v>3.1870755</v>
+        <v>3.16576225</v>
       </c>
       <c r="P68">
-        <v>9.5612265</v>
+        <v>9.497286750000001</v>
       </c>
       <c r="Q68">
-        <v>14.0612265</v>
+        <v>13.99728675</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1950181082172989</v>
+        <v>0.1990795700631698</v>
       </c>
       <c r="T68">
-        <v>2.17130529129678</v>
+        <v>2.23040450989495</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.265680866469108</v>
+        <v>3.216939360999421</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09790650812084604</v>
+        <v>0.09777735944781046</v>
       </c>
       <c r="C69">
-        <v>56.46190178647835</v>
+        <v>55.45235958101718</v>
       </c>
       <c r="D69">
-        <v>128.9719017864784</v>
+        <v>129.2923595810172</v>
       </c>
       <c r="E69">
-        <v>14.20999999999999</v>
+        <v>15.54000000000001</v>
       </c>
       <c r="F69">
-        <v>89.11</v>
+        <v>90.44000000000001</v>
       </c>
       <c r="G69">
         <v>16.6</v>
@@ -6933,28 +6933,28 @@
         <v>18.375</v>
       </c>
       <c r="M69">
-        <v>5.711951</v>
+        <v>5.797204000000002</v>
       </c>
       <c r="N69">
-        <v>12.663049</v>
+        <v>12.577796</v>
       </c>
       <c r="O69">
-        <v>3.16576225</v>
+        <v>3.144449</v>
       </c>
       <c r="P69">
-        <v>9.497286750000001</v>
+        <v>9.433346999999999</v>
       </c>
       <c r="Q69">
-        <v>13.99728675</v>
+        <v>13.933347</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1990795700631698</v>
+        <v>0.2033948732744077</v>
       </c>
       <c r="T69">
-        <v>2.23040450989495</v>
+        <v>2.293197429655506</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.216939360999421</v>
+        <v>3.169631429220016</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09777735944781046</v>
+        <v>0.0976482107747749</v>
       </c>
       <c r="C70">
-        <v>55.45235958101718</v>
+        <v>54.44441383176195</v>
       </c>
       <c r="D70">
-        <v>129.2923595810172</v>
+        <v>129.614413831762</v>
       </c>
       <c r="E70">
-        <v>15.54000000000001</v>
+        <v>16.87</v>
       </c>
       <c r="F70">
-        <v>90.44000000000001</v>
+        <v>91.77000000000001</v>
       </c>
       <c r="G70">
         <v>16.6</v>
@@ -7015,28 +7015,28 @@
         <v>18.375</v>
       </c>
       <c r="M70">
-        <v>5.797204000000002</v>
+        <v>5.882457000000001</v>
       </c>
       <c r="N70">
-        <v>12.577796</v>
+        <v>12.492543</v>
       </c>
       <c r="O70">
-        <v>3.144449</v>
+        <v>3.123135749999999</v>
       </c>
       <c r="P70">
-        <v>9.433346999999999</v>
+        <v>9.369407249999998</v>
       </c>
       <c r="Q70">
-        <v>13.933347</v>
+        <v>13.86940725</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2033948732744077</v>
+        <v>0.2079885831444352</v>
       </c>
       <c r="T70">
-        <v>2.293197429655506</v>
+        <v>2.360041505529647</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.169631429220016</v>
+        <v>3.123694741840016</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0976482107747749</v>
+        <v>0.09751906210173933</v>
       </c>
       <c r="C71">
-        <v>54.44441383176195</v>
+        <v>53.43807649833788</v>
       </c>
       <c r="D71">
-        <v>129.614413831762</v>
+        <v>129.9380764983379</v>
       </c>
       <c r="E71">
-        <v>16.87</v>
+        <v>18.2</v>
       </c>
       <c r="F71">
-        <v>91.77000000000001</v>
+        <v>93.10000000000001</v>
       </c>
       <c r="G71">
         <v>16.6</v>
@@ -7097,28 +7097,28 @@
         <v>18.375</v>
       </c>
       <c r="M71">
-        <v>5.882457000000001</v>
+        <v>5.967710000000001</v>
       </c>
       <c r="N71">
-        <v>12.492543</v>
+        <v>12.40729</v>
       </c>
       <c r="O71">
-        <v>3.123135749999999</v>
+        <v>3.1018225</v>
       </c>
       <c r="P71">
-        <v>9.369407249999998</v>
+        <v>9.305467499999999</v>
       </c>
       <c r="Q71">
-        <v>13.86940725</v>
+        <v>13.8054675</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2079885831444352</v>
+        <v>0.2128885403391311</v>
       </c>
       <c r="T71">
-        <v>2.360041505529647</v>
+        <v>2.43134185312873</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.123694741840016</v>
+        <v>3.079070531242302</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09751906210173933</v>
+        <v>0.09738991342870376</v>
       </c>
       <c r="C72">
-        <v>53.43807649833788</v>
+        <v>52.43335966012773</v>
       </c>
       <c r="D72">
-        <v>129.9380764983379</v>
+        <v>130.2633596601277</v>
       </c>
       <c r="E72">
-        <v>18.2</v>
+        <v>19.53</v>
       </c>
       <c r="F72">
-        <v>93.10000000000001</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="G72">
         <v>16.6</v>
@@ -7179,28 +7179,28 @@
         <v>18.375</v>
       </c>
       <c r="M72">
-        <v>5.967710000000001</v>
+        <v>6.052963000000001</v>
       </c>
       <c r="N72">
-        <v>12.40729</v>
+        <v>12.322037</v>
       </c>
       <c r="O72">
-        <v>3.1018225</v>
+        <v>3.08050925</v>
       </c>
       <c r="P72">
-        <v>9.305467499999999</v>
+        <v>9.241527749999999</v>
       </c>
       <c r="Q72">
-        <v>13.8054675</v>
+        <v>13.74152775</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2128885403391311</v>
+        <v>0.2181264256162199</v>
       </c>
       <c r="T72">
-        <v>2.43134185312873</v>
+        <v>2.507559466079474</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.079070531242302</v>
+        <v>3.035703340661424</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09738991342870375</v>
+        <v>0.1014727647556682</v>
       </c>
       <c r="C73">
-        <v>52.43335966012781</v>
+        <v>41.55028764767582</v>
       </c>
       <c r="D73">
-        <v>130.2633596601278</v>
+        <v>120.7102876476758</v>
       </c>
       <c r="E73">
-        <v>19.52999999999999</v>
+        <v>20.85999999999999</v>
       </c>
       <c r="F73">
-        <v>94.42999999999999</v>
+        <v>95.75999999999999</v>
       </c>
       <c r="G73">
         <v>16.6</v>
@@ -7261,45 +7261,45 @@
         <v>18.375</v>
       </c>
       <c r="M73">
-        <v>6.052963</v>
+        <v>6.885143999999999</v>
       </c>
       <c r="N73">
-        <v>12.322037</v>
+        <v>11.489856</v>
       </c>
       <c r="O73">
-        <v>3.08050925</v>
+        <v>2.872464</v>
       </c>
       <c r="P73">
-        <v>9.241527749999999</v>
+        <v>8.617391999999999</v>
       </c>
       <c r="Q73">
-        <v>13.74152775</v>
+        <v>13.117392</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2181264256162198</v>
+        <v>0.2237384455559577</v>
       </c>
       <c r="T73">
-        <v>2.507559466079473</v>
+        <v>2.589221194240984</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.035703340661425</v>
+        <v>2.668789498084572</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1014727647556682</v>
+        <v>0.1014021160826326</v>
       </c>
       <c r="C74">
-        <v>41.55028764767582</v>
+        <v>40.37366349458381</v>
       </c>
       <c r="D74">
-        <v>120.7102876476758</v>
+        <v>120.8636634945838</v>
       </c>
       <c r="E74">
-        <v>20.85999999999999</v>
+        <v>22.19</v>
       </c>
       <c r="F74">
-        <v>95.75999999999999</v>
+        <v>97.09</v>
       </c>
       <c r="G74">
         <v>16.6</v>
@@ -7343,28 +7343,28 @@
         <v>18.375</v>
       </c>
       <c r="M74">
-        <v>6.885143999999999</v>
+        <v>6.980771000000001</v>
       </c>
       <c r="N74">
-        <v>11.489856</v>
+        <v>11.394229</v>
       </c>
       <c r="O74">
-        <v>2.872464</v>
+        <v>2.84855725</v>
       </c>
       <c r="P74">
-        <v>8.617391999999999</v>
+        <v>8.54567175</v>
       </c>
       <c r="Q74">
-        <v>13.117392</v>
+        <v>13.04567175</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2237384455559577</v>
+        <v>0.229766170676417</v>
       </c>
       <c r="T74">
-        <v>2.589221194240984</v>
+        <v>2.676931939303349</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.668789498084572</v>
+        <v>2.632230737836838</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1014021160826326</v>
+        <v>0.101331467409597</v>
       </c>
       <c r="C75">
-        <v>40.37366349458381</v>
+        <v>39.19742959950464</v>
       </c>
       <c r="D75">
-        <v>120.8636634945838</v>
+        <v>121.0174295995046</v>
       </c>
       <c r="E75">
-        <v>22.19</v>
+        <v>23.52</v>
       </c>
       <c r="F75">
-        <v>97.09</v>
+        <v>98.42</v>
       </c>
       <c r="G75">
         <v>16.6</v>
@@ -7425,28 +7425,28 @@
         <v>18.375</v>
       </c>
       <c r="M75">
-        <v>6.980771000000001</v>
+        <v>7.076398000000001</v>
       </c>
       <c r="N75">
-        <v>11.394229</v>
+        <v>11.298602</v>
       </c>
       <c r="O75">
-        <v>2.84855725</v>
+        <v>2.8246505</v>
       </c>
       <c r="P75">
-        <v>8.54567175</v>
+        <v>8.473951499999998</v>
       </c>
       <c r="Q75">
-        <v>13.04567175</v>
+        <v>12.9739515</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.229766170676417</v>
+        <v>0.2362575669599885</v>
       </c>
       <c r="T75">
-        <v>2.676931939303349</v>
+        <v>2.771389664755125</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.632230737836838</v>
+        <v>2.596660052190394</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.101331467409597</v>
+        <v>0.1012608187365615</v>
       </c>
       <c r="C76">
-        <v>39.19742959950464</v>
+        <v>38.02158745382681</v>
       </c>
       <c r="D76">
-        <v>121.0174295995046</v>
+        <v>121.1715874538268</v>
       </c>
       <c r="E76">
-        <v>23.52</v>
+        <v>24.84999999999999</v>
       </c>
       <c r="F76">
-        <v>98.42</v>
+        <v>99.75</v>
       </c>
       <c r="G76">
         <v>16.6</v>
@@ -7507,28 +7507,28 @@
         <v>18.375</v>
       </c>
       <c r="M76">
-        <v>7.076398000000001</v>
+        <v>7.172025000000001</v>
       </c>
       <c r="N76">
-        <v>11.298602</v>
+        <v>11.202975</v>
       </c>
       <c r="O76">
-        <v>2.8246505</v>
+        <v>2.80074375</v>
       </c>
       <c r="P76">
-        <v>8.473951499999998</v>
+        <v>8.40223125</v>
       </c>
       <c r="Q76">
-        <v>12.9739515</v>
+        <v>12.90223125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2362575669599885</v>
+        <v>0.2432682749462458</v>
       </c>
       <c r="T76">
-        <v>2.771389664755125</v>
+        <v>2.873404008243044</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.596660052190394</v>
+        <v>2.562037918161189</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1012608187365615</v>
+        <v>0.1011901700635259</v>
       </c>
       <c r="C77">
-        <v>38.02158745382681</v>
+        <v>36.84613855654793</v>
       </c>
       <c r="D77">
-        <v>121.1715874538268</v>
+        <v>121.3261385565479</v>
       </c>
       <c r="E77">
-        <v>24.84999999999999</v>
+        <v>26.17999999999999</v>
       </c>
       <c r="F77">
-        <v>99.75</v>
+        <v>101.08</v>
       </c>
       <c r="G77">
         <v>16.6</v>
@@ -7589,28 +7589,28 @@
         <v>18.375</v>
       </c>
       <c r="M77">
-        <v>7.172025000000001</v>
+        <v>7.267652</v>
       </c>
       <c r="N77">
-        <v>11.202975</v>
+        <v>11.107348</v>
       </c>
       <c r="O77">
-        <v>2.80074375</v>
+        <v>2.776837</v>
       </c>
       <c r="P77">
-        <v>8.40223125</v>
+        <v>8.330511</v>
       </c>
       <c r="Q77">
-        <v>12.90223125</v>
+        <v>12.830511</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2432682749462458</v>
+        <v>0.2508632085980245</v>
       </c>
       <c r="T77">
-        <v>2.873404008243044</v>
+        <v>2.983919547021622</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.562037918161189</v>
+        <v>2.528326892922226</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1011901700635259</v>
+        <v>0.1033717713904903</v>
       </c>
       <c r="C78">
-        <v>36.84613855654793</v>
+        <v>30.91865512885968</v>
       </c>
       <c r="D78">
-        <v>121.3261385565479</v>
+        <v>116.7286551288597</v>
       </c>
       <c r="E78">
-        <v>26.17999999999999</v>
+        <v>27.50999999999999</v>
       </c>
       <c r="F78">
-        <v>101.08</v>
+        <v>102.41</v>
       </c>
       <c r="G78">
         <v>16.6</v>
@@ -7671,45 +7671,45 @@
         <v>18.375</v>
       </c>
       <c r="M78">
-        <v>7.267652</v>
+        <v>7.762678</v>
       </c>
       <c r="N78">
-        <v>11.107348</v>
+        <v>10.612322</v>
       </c>
       <c r="O78">
-        <v>2.776837</v>
+        <v>2.6530805</v>
       </c>
       <c r="P78">
-        <v>8.330511</v>
+        <v>7.959241499999999</v>
       </c>
       <c r="Q78">
-        <v>12.830511</v>
+        <v>12.4592415</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2508632085980245</v>
+        <v>0.2591185712630013</v>
       </c>
       <c r="T78">
-        <v>2.983919547021622</v>
+        <v>3.104045132650513</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.528326892922226</v>
+        <v>2.367095479163247</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1033717713904903</v>
+        <v>0.1033303727174547</v>
       </c>
       <c r="C79">
-        <v>30.91865512885968</v>
+        <v>29.67265269743609</v>
       </c>
       <c r="D79">
-        <v>116.7286551288597</v>
+        <v>116.8126526974361</v>
       </c>
       <c r="E79">
-        <v>27.50999999999999</v>
+        <v>28.84</v>
       </c>
       <c r="F79">
-        <v>102.41</v>
+        <v>103.74</v>
       </c>
       <c r="G79">
         <v>16.6</v>
@@ -7753,28 +7753,28 @@
         <v>18.375</v>
       </c>
       <c r="M79">
-        <v>7.762678</v>
+        <v>7.863492000000002</v>
       </c>
       <c r="N79">
-        <v>10.612322</v>
+        <v>10.511508</v>
       </c>
       <c r="O79">
-        <v>2.6530805</v>
+        <v>2.627877</v>
       </c>
       <c r="P79">
-        <v>7.959241499999999</v>
+        <v>7.883630999999999</v>
       </c>
       <c r="Q79">
-        <v>12.4592415</v>
+        <v>12.383631</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2591185712630013</v>
+        <v>0.268124421442976</v>
       </c>
       <c r="T79">
-        <v>3.104045132650513</v>
+        <v>3.235091226063847</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.367095479163247</v>
+        <v>2.336748101225257</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1033303727174547</v>
+        <v>0.1032889740444191</v>
       </c>
       <c r="C80">
-        <v>29.67265269743609</v>
+        <v>28.42677124183218</v>
       </c>
       <c r="D80">
-        <v>116.8126526974361</v>
+        <v>116.8967712418322</v>
       </c>
       <c r="E80">
-        <v>28.84</v>
+        <v>30.17</v>
       </c>
       <c r="F80">
-        <v>103.74</v>
+        <v>105.07</v>
       </c>
       <c r="G80">
         <v>16.6</v>
@@ -7835,28 +7835,28 @@
         <v>18.375</v>
       </c>
       <c r="M80">
-        <v>7.863492000000002</v>
+        <v>7.964306000000001</v>
       </c>
       <c r="N80">
-        <v>10.511508</v>
+        <v>10.410694</v>
       </c>
       <c r="O80">
-        <v>2.627877</v>
+        <v>2.6026735</v>
       </c>
       <c r="P80">
-        <v>7.883630999999999</v>
+        <v>7.8080205</v>
       </c>
       <c r="Q80">
-        <v>12.383631</v>
+        <v>12.3080205</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.268124421442976</v>
+        <v>0.2779879716400912</v>
       </c>
       <c r="T80">
-        <v>3.235091226063847</v>
+        <v>3.378617899802261</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.336748101225257</v>
+        <v>2.307169011336329</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1032889740444191</v>
+        <v>0.1032475753713836</v>
       </c>
       <c r="C81">
-        <v>28.42677124183218</v>
+        <v>27.18101102358571</v>
       </c>
       <c r="D81">
-        <v>116.8967712418322</v>
+        <v>116.9810110235857</v>
       </c>
       <c r="E81">
-        <v>30.17</v>
+        <v>31.5</v>
       </c>
       <c r="F81">
-        <v>105.07</v>
+        <v>106.4</v>
       </c>
       <c r="G81">
         <v>16.6</v>
@@ -7917,28 +7917,28 @@
         <v>18.375</v>
       </c>
       <c r="M81">
-        <v>7.964306000000001</v>
+        <v>8.06512</v>
       </c>
       <c r="N81">
-        <v>10.410694</v>
+        <v>10.30988</v>
       </c>
       <c r="O81">
-        <v>2.6026735</v>
+        <v>2.57747</v>
       </c>
       <c r="P81">
-        <v>7.8080205</v>
+        <v>7.73241</v>
       </c>
       <c r="Q81">
-        <v>12.3080205</v>
+        <v>12.23241</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2779879716400912</v>
+        <v>0.2888378768569179</v>
       </c>
       <c r="T81">
-        <v>3.378617899802261</v>
+        <v>3.536497240914517</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.307169011336329</v>
+        <v>2.278329398694626</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1032475753713836</v>
+        <v>0.103206176698348</v>
       </c>
       <c r="C82">
-        <v>27.18101102358571</v>
+        <v>25.935372304989</v>
       </c>
       <c r="D82">
-        <v>116.9810110235857</v>
+        <v>117.065372304989</v>
       </c>
       <c r="E82">
-        <v>31.5</v>
+        <v>32.83</v>
       </c>
       <c r="F82">
-        <v>106.4</v>
+        <v>107.73</v>
       </c>
       <c r="G82">
         <v>16.6</v>
@@ -7999,28 +7999,28 @@
         <v>18.375</v>
       </c>
       <c r="M82">
-        <v>8.06512</v>
+        <v>8.165934000000002</v>
       </c>
       <c r="N82">
-        <v>10.30988</v>
+        <v>10.209066</v>
       </c>
       <c r="O82">
-        <v>2.57747</v>
+        <v>2.5522665</v>
       </c>
       <c r="P82">
-        <v>7.73241</v>
+        <v>7.656799499999998</v>
       </c>
       <c r="Q82">
-        <v>12.23241</v>
+        <v>12.1567995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2888378768569179</v>
+        <v>0.3008298773597264</v>
       </c>
       <c r="T82">
-        <v>3.536497240914517</v>
+        <v>3.710995460038588</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.278329398694626</v>
+        <v>2.250201875253951</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.103206176698348</v>
+        <v>0.1031647780253124</v>
       </c>
       <c r="C83">
-        <v>25.935372304989</v>
+        <v>24.68985534909149</v>
       </c>
       <c r="D83">
-        <v>117.065372304989</v>
+        <v>117.1498553490915</v>
       </c>
       <c r="E83">
-        <v>32.83</v>
+        <v>34.16</v>
       </c>
       <c r="F83">
-        <v>107.73</v>
+        <v>109.06</v>
       </c>
       <c r="G83">
         <v>16.6</v>
@@ -8081,28 +8081,28 @@
         <v>18.375</v>
       </c>
       <c r="M83">
-        <v>8.165934000000002</v>
+        <v>8.266748000000002</v>
       </c>
       <c r="N83">
-        <v>10.209066</v>
+        <v>10.108252</v>
       </c>
       <c r="O83">
-        <v>2.5522665</v>
+        <v>2.527063</v>
       </c>
       <c r="P83">
-        <v>7.656799499999998</v>
+        <v>7.581188999999998</v>
       </c>
       <c r="Q83">
-        <v>12.1567995</v>
+        <v>12.081189</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3008298773597264</v>
+        <v>0.3141543223628469</v>
       </c>
       <c r="T83">
-        <v>3.710995460038588</v>
+        <v>3.904882370176445</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.250201875253951</v>
+        <v>2.222760388970366</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1031647780253124</v>
+        <v>0.1031233793522769</v>
       </c>
       <c r="C84">
-        <v>24.68985534909149</v>
+        <v>23.44446041970249</v>
       </c>
       <c r="D84">
-        <v>117.1498553490915</v>
+        <v>117.2344604197025</v>
       </c>
       <c r="E84">
-        <v>34.16</v>
+        <v>35.49000000000001</v>
       </c>
       <c r="F84">
-        <v>109.06</v>
+        <v>110.39</v>
       </c>
       <c r="G84">
         <v>16.6</v>
@@ -8163,28 +8163,28 @@
         <v>18.375</v>
       </c>
       <c r="M84">
-        <v>8.266748000000002</v>
+        <v>8.367562000000001</v>
       </c>
       <c r="N84">
-        <v>10.108252</v>
+        <v>10.007438</v>
       </c>
       <c r="O84">
-        <v>2.527063</v>
+        <v>2.5018595</v>
       </c>
       <c r="P84">
-        <v>7.581188999999998</v>
+        <v>7.505578499999999</v>
       </c>
       <c r="Q84">
-        <v>12.081189</v>
+        <v>12.0055785</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3141543223628469</v>
+        <v>0.3290463491310405</v>
       </c>
       <c r="T84">
-        <v>3.904882370176445</v>
+        <v>4.121579505036404</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.222760388970366</v>
+        <v>2.195980143320121</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1031233793522769</v>
+        <v>0.1030819806792413</v>
       </c>
       <c r="C85">
-        <v>23.44446041970249</v>
+        <v>22.199187781394</v>
       </c>
       <c r="D85">
-        <v>117.2344604197025</v>
+        <v>117.319187781394</v>
       </c>
       <c r="E85">
-        <v>35.49000000000001</v>
+        <v>36.82000000000001</v>
       </c>
       <c r="F85">
-        <v>110.39</v>
+        <v>111.72</v>
       </c>
       <c r="G85">
         <v>16.6</v>
@@ -8245,28 +8245,28 @@
         <v>18.375</v>
       </c>
       <c r="M85">
-        <v>8.367562000000001</v>
+        <v>8.468376000000001</v>
       </c>
       <c r="N85">
-        <v>10.007438</v>
+        <v>9.906623999999999</v>
       </c>
       <c r="O85">
-        <v>2.5018595</v>
+        <v>2.476656</v>
       </c>
       <c r="P85">
-        <v>7.505578499999999</v>
+        <v>7.429967999999999</v>
       </c>
       <c r="Q85">
-        <v>12.0055785</v>
+        <v>11.929968</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3290463491310405</v>
+        <v>0.3457998792452582</v>
       </c>
       <c r="T85">
-        <v>4.121579505036404</v>
+        <v>4.365363781753858</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.195980143320121</v>
+        <v>2.16983752256631</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1030819806792413</v>
+        <v>0.1030405820062057</v>
       </c>
       <c r="C86">
-        <v>22.19918778139402</v>
+        <v>20.95403769950342</v>
       </c>
       <c r="D86">
-        <v>117.319187781394</v>
+        <v>117.4040376995034</v>
       </c>
       <c r="E86">
-        <v>36.81999999999999</v>
+        <v>38.14999999999999</v>
       </c>
       <c r="F86">
-        <v>111.72</v>
+        <v>113.05</v>
       </c>
       <c r="G86">
         <v>16.6</v>
@@ -8327,28 +8327,28 @@
         <v>18.375</v>
       </c>
       <c r="M86">
-        <v>8.468376000000001</v>
+        <v>8.569190000000001</v>
       </c>
       <c r="N86">
-        <v>9.906623999999999</v>
+        <v>9.805809999999999</v>
       </c>
       <c r="O86">
-        <v>2.476656</v>
+        <v>2.4514525</v>
       </c>
       <c r="P86">
-        <v>7.429967999999999</v>
+        <v>7.354357499999999</v>
       </c>
       <c r="Q86">
-        <v>11.929968</v>
+        <v>11.8543575</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.345799879245258</v>
+        <v>0.3647872133747048</v>
       </c>
       <c r="T86">
-        <v>4.365363781753855</v>
+        <v>4.641652628700302</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.16983752256631</v>
+        <v>2.144310022300824</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1030405820062057</v>
+        <v>0.1029991833331701</v>
       </c>
       <c r="C87">
-        <v>20.95403769950342</v>
+        <v>19.70901044013624</v>
       </c>
       <c r="D87">
-        <v>117.4040376995034</v>
+        <v>117.4890104401362</v>
       </c>
       <c r="E87">
-        <v>38.14999999999999</v>
+        <v>39.47999999999999</v>
       </c>
       <c r="F87">
-        <v>113.05</v>
+        <v>114.38</v>
       </c>
       <c r="G87">
         <v>16.6</v>
@@ -8409,28 +8409,28 @@
         <v>18.375</v>
       </c>
       <c r="M87">
-        <v>8.569190000000001</v>
+        <v>8.670004</v>
       </c>
       <c r="N87">
-        <v>9.805809999999999</v>
+        <v>9.704996</v>
       </c>
       <c r="O87">
-        <v>2.4514525</v>
+        <v>2.426249</v>
       </c>
       <c r="P87">
-        <v>7.354357499999999</v>
+        <v>7.278746999999999</v>
       </c>
       <c r="Q87">
-        <v>11.8543575</v>
+        <v>11.778747</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3647872133747048</v>
+        <v>0.3864870238083581</v>
       </c>
       <c r="T87">
-        <v>4.641652628700302</v>
+        <v>4.957411310924812</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.144310022300824</v>
+        <v>2.11937618483221</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1029991833331701</v>
+        <v>0.1029577846601346</v>
       </c>
       <c r="C88">
-        <v>19.70901044013624</v>
+        <v>18.46410627016895</v>
       </c>
       <c r="D88">
-        <v>117.4890104401362</v>
+        <v>117.574106270169</v>
       </c>
       <c r="E88">
-        <v>39.47999999999999</v>
+        <v>40.80999999999999</v>
       </c>
       <c r="F88">
-        <v>114.38</v>
+        <v>115.71</v>
       </c>
       <c r="G88">
         <v>16.6</v>
@@ -8491,28 +8491,28 @@
         <v>18.375</v>
       </c>
       <c r="M88">
-        <v>8.670004</v>
+        <v>8.770818</v>
       </c>
       <c r="N88">
-        <v>9.704996</v>
+        <v>9.604182</v>
       </c>
       <c r="O88">
-        <v>2.426249</v>
+        <v>2.4010455</v>
       </c>
       <c r="P88">
-        <v>7.278746999999999</v>
+        <v>7.203136499999999</v>
       </c>
       <c r="Q88">
-        <v>11.778747</v>
+        <v>11.7031365</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3864870238083581</v>
+        <v>0.4115252666164196</v>
       </c>
       <c r="T88">
-        <v>4.957411310924812</v>
+        <v>5.321748251953093</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.11937618483221</v>
+        <v>2.095015539029541</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1029577846601346</v>
+        <v>0.102916385987099</v>
       </c>
       <c r="C89">
-        <v>18.46410627016895</v>
+        <v>17.21932545725174</v>
       </c>
       <c r="D89">
-        <v>117.574106270169</v>
+        <v>117.6593254572517</v>
       </c>
       <c r="E89">
-        <v>40.80999999999999</v>
+        <v>42.14</v>
       </c>
       <c r="F89">
-        <v>115.71</v>
+        <v>117.04</v>
       </c>
       <c r="G89">
         <v>16.6</v>
@@ -8573,28 +8573,28 @@
         <v>18.375</v>
       </c>
       <c r="M89">
-        <v>8.770818</v>
+        <v>8.871632000000002</v>
       </c>
       <c r="N89">
-        <v>9.604182</v>
+        <v>9.503367999999998</v>
       </c>
       <c r="O89">
-        <v>2.4010455</v>
+        <v>2.375842</v>
       </c>
       <c r="P89">
-        <v>7.203136499999999</v>
+        <v>7.127525999999999</v>
       </c>
       <c r="Q89">
-        <v>11.7031365</v>
+        <v>11.627526</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4115252666164196</v>
+        <v>0.4407365498924916</v>
       </c>
       <c r="T89">
-        <v>5.321748251953093</v>
+        <v>5.746808016486088</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.095015539029541</v>
+        <v>2.071208544267841</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.102916385987099</v>
+        <v>0.1028749873140634</v>
       </c>
       <c r="C90">
-        <v>17.21932545725174</v>
+        <v>15.97466826981142</v>
       </c>
       <c r="D90">
-        <v>117.6593254572517</v>
+        <v>117.7446682698114</v>
       </c>
       <c r="E90">
-        <v>42.14</v>
+        <v>43.47</v>
       </c>
       <c r="F90">
-        <v>117.04</v>
+        <v>118.37</v>
       </c>
       <c r="G90">
         <v>16.6</v>
@@ -8655,28 +8655,28 @@
         <v>18.375</v>
       </c>
       <c r="M90">
-        <v>8.871632000000002</v>
+        <v>8.972446000000001</v>
       </c>
       <c r="N90">
-        <v>9.503367999999998</v>
+        <v>9.402553999999999</v>
       </c>
       <c r="O90">
-        <v>2.375842</v>
+        <v>2.3506385</v>
       </c>
       <c r="P90">
-        <v>7.127525999999999</v>
+        <v>7.051915499999999</v>
       </c>
       <c r="Q90">
-        <v>11.627526</v>
+        <v>11.5519155</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4407365498924916</v>
+        <v>0.4752589755823947</v>
       </c>
       <c r="T90">
-        <v>5.746808016486088</v>
+        <v>6.249151374570537</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.071208544267841</v>
+        <v>2.047936538152472</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1028749873140634</v>
+        <v>0.1028335886410278</v>
       </c>
       <c r="C91">
-        <v>15.97466826981142</v>
+        <v>14.73013497705413</v>
       </c>
       <c r="D91">
-        <v>117.7446682698114</v>
+        <v>117.8301349770541</v>
       </c>
       <c r="E91">
-        <v>43.47</v>
+        <v>44.8</v>
       </c>
       <c r="F91">
-        <v>118.37</v>
+        <v>119.7</v>
       </c>
       <c r="G91">
         <v>16.6</v>
@@ -8737,28 +8737,28 @@
         <v>18.375</v>
       </c>
       <c r="M91">
-        <v>8.972446000000001</v>
+        <v>9.073260000000001</v>
       </c>
       <c r="N91">
-        <v>9.402553999999999</v>
+        <v>9.301739999999999</v>
       </c>
       <c r="O91">
-        <v>2.3506385</v>
+        <v>2.325435</v>
       </c>
       <c r="P91">
-        <v>7.051915499999999</v>
+        <v>6.976304999999999</v>
       </c>
       <c r="Q91">
-        <v>11.5519155</v>
+        <v>11.476305</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4752589755823947</v>
+        <v>0.5166858864102785</v>
       </c>
       <c r="T91">
-        <v>6.249151374570537</v>
+        <v>6.851963404271876</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.047936538152472</v>
+        <v>2.025181687728556</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1028335886410278</v>
+        <v>0.1027921899679923</v>
       </c>
       <c r="C92">
-        <v>14.73013497705413</v>
+        <v>13.48572584896823</v>
       </c>
       <c r="D92">
-        <v>117.8301349770541</v>
+        <v>117.9157258489682</v>
       </c>
       <c r="E92">
-        <v>44.8</v>
+        <v>46.13</v>
       </c>
       <c r="F92">
-        <v>119.7</v>
+        <v>121.03</v>
       </c>
       <c r="G92">
         <v>16.6</v>
@@ -8819,28 +8819,28 @@
         <v>18.375</v>
       </c>
       <c r="M92">
-        <v>9.073260000000001</v>
+        <v>9.174074000000001</v>
       </c>
       <c r="N92">
-        <v>9.301739999999999</v>
+        <v>9.200925999999999</v>
       </c>
       <c r="O92">
-        <v>2.325435</v>
+        <v>2.3002315</v>
       </c>
       <c r="P92">
-        <v>6.976304999999999</v>
+        <v>6.900694499999999</v>
       </c>
       <c r="Q92">
-        <v>11.476305</v>
+        <v>11.4006945</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5166858864102785</v>
+        <v>0.5673187774221363</v>
       </c>
       <c r="T92">
-        <v>6.851963404271876</v>
+        <v>7.588733662795733</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.025181687728556</v>
+        <v>2.002926943907363</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1027921899679923</v>
+        <v>0.1125487912949567</v>
       </c>
       <c r="C93">
-        <v>13.48572584896823</v>
+        <v>-5.079893028447216</v>
       </c>
       <c r="D93">
-        <v>117.9157258489682</v>
+        <v>100.6801069715528</v>
       </c>
       <c r="E93">
-        <v>46.13</v>
+        <v>47.45999999999999</v>
       </c>
       <c r="F93">
-        <v>121.03</v>
+        <v>122.36</v>
       </c>
       <c r="G93">
         <v>16.6</v>
@@ -8901,45 +8901,45 @@
         <v>18.375</v>
       </c>
       <c r="M93">
-        <v>9.174074000000001</v>
+        <v>11.0124</v>
       </c>
       <c r="N93">
-        <v>9.200925999999999</v>
+        <v>7.3626</v>
       </c>
       <c r="O93">
-        <v>2.3002315</v>
+        <v>1.84065</v>
       </c>
       <c r="P93">
-        <v>6.900694499999999</v>
+        <v>5.52195</v>
       </c>
       <c r="Q93">
-        <v>11.4006945</v>
+        <v>10.02195</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5673187774221363</v>
+        <v>0.630609891186959</v>
       </c>
       <c r="T93">
-        <v>7.588733662795733</v>
+        <v>8.509696485950558</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.002926943907363</v>
+        <v>1.668573607932876</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1125487912949567</v>
+        <v>0.1126138926219211</v>
       </c>
       <c r="C94">
-        <v>-5.079893028447216</v>
+        <v>-6.507992515029414</v>
       </c>
       <c r="D94">
-        <v>100.6801069715528</v>
+        <v>100.5820074849706</v>
       </c>
       <c r="E94">
-        <v>47.45999999999999</v>
+        <v>48.79000000000001</v>
       </c>
       <c r="F94">
-        <v>122.36</v>
+        <v>123.69</v>
       </c>
       <c r="G94">
         <v>16.6</v>
@@ -8983,28 +8983,28 @@
         <v>18.375</v>
       </c>
       <c r="M94">
-        <v>11.0124</v>
+        <v>11.1321</v>
       </c>
       <c r="N94">
-        <v>7.3626</v>
+        <v>7.242899999999999</v>
       </c>
       <c r="O94">
-        <v>1.84065</v>
+        <v>1.810725</v>
       </c>
       <c r="P94">
-        <v>5.52195</v>
+        <v>5.432174999999999</v>
       </c>
       <c r="Q94">
-        <v>10.02195</v>
+        <v>9.932174999999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.630609891186959</v>
+        <v>0.7119841803131592</v>
       </c>
       <c r="T94">
-        <v>8.509696485950558</v>
+        <v>9.693791544292473</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.668573607932876</v>
+        <v>1.650631956234673</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1126138926219211</v>
+        <v>0.1126789939488855</v>
       </c>
       <c r="C95">
-        <v>-6.507992515029414</v>
+        <v>-7.935901017675548</v>
       </c>
       <c r="D95">
-        <v>100.5820074849706</v>
+        <v>100.4840989823245</v>
       </c>
       <c r="E95">
-        <v>48.79000000000001</v>
+        <v>50.12</v>
       </c>
       <c r="F95">
-        <v>123.69</v>
+        <v>125.02</v>
       </c>
       <c r="G95">
         <v>16.6</v>
@@ -9065,28 +9065,28 @@
         <v>18.375</v>
       </c>
       <c r="M95">
-        <v>11.1321</v>
+        <v>11.2518</v>
       </c>
       <c r="N95">
-        <v>7.242899999999999</v>
+        <v>7.123199999999999</v>
       </c>
       <c r="O95">
-        <v>1.810725</v>
+        <v>1.7808</v>
       </c>
       <c r="P95">
-        <v>5.432174999999999</v>
+        <v>5.3424</v>
       </c>
       <c r="Q95">
-        <v>9.932174999999999</v>
+        <v>9.8424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7119841803131592</v>
+        <v>0.8204832324814263</v>
       </c>
       <c r="T95">
-        <v>9.693791544292473</v>
+        <v>11.27258495541503</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.650631956234673</v>
+        <v>1.633072041806644</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1126789939488855</v>
+        <v>0.11274409527585</v>
       </c>
       <c r="C96">
-        <v>-7.935901017675548</v>
+        <v>-9.363619093565902</v>
       </c>
       <c r="D96">
-        <v>100.4840989823245</v>
+        <v>100.3863809064341</v>
       </c>
       <c r="E96">
-        <v>50.12</v>
+        <v>51.45</v>
       </c>
       <c r="F96">
-        <v>125.02</v>
+        <v>126.35</v>
       </c>
       <c r="G96">
         <v>16.6</v>
@@ -9147,28 +9147,28 @@
         <v>18.375</v>
       </c>
       <c r="M96">
-        <v>11.2518</v>
+        <v>11.3715</v>
       </c>
       <c r="N96">
-        <v>7.123199999999999</v>
+        <v>7.003499999999999</v>
       </c>
       <c r="O96">
-        <v>1.7808</v>
+        <v>1.750875</v>
       </c>
       <c r="P96">
-        <v>5.3424</v>
+        <v>5.252624999999999</v>
       </c>
       <c r="Q96">
-        <v>9.8424</v>
+        <v>9.752624999999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8204832324814263</v>
+        <v>0.9723819055170007</v>
       </c>
       <c r="T96">
-        <v>11.27258495541503</v>
+        <v>13.48289573098661</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.633072041806644</v>
+        <v>1.615881809787627</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.11274409527585</v>
+        <v>0.1128091966028144</v>
       </c>
       <c r="C97">
-        <v>-9.363619093565902</v>
+        <v>-10.79114729771527</v>
       </c>
       <c r="D97">
-        <v>100.3863809064341</v>
+        <v>100.2888527022847</v>
       </c>
       <c r="E97">
-        <v>51.45</v>
+        <v>52.78</v>
       </c>
       <c r="F97">
-        <v>126.35</v>
+        <v>127.68</v>
       </c>
       <c r="G97">
         <v>16.6</v>
@@ -9229,28 +9229,28 @@
         <v>18.375</v>
       </c>
       <c r="M97">
-        <v>11.3715</v>
+        <v>11.4912</v>
       </c>
       <c r="N97">
-        <v>7.003499999999999</v>
+        <v>6.883799999999999</v>
       </c>
       <c r="O97">
-        <v>1.750875</v>
+        <v>1.72095</v>
       </c>
       <c r="P97">
-        <v>5.252624999999999</v>
+        <v>5.162849999999999</v>
       </c>
       <c r="Q97">
-        <v>9.752624999999998</v>
+        <v>9.662849999999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9723819055170007</v>
+        <v>1.200229915070362</v>
       </c>
       <c r="T97">
-        <v>13.48289573098661</v>
+        <v>16.79836189434398</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.615881809787627</v>
+        <v>1.599049707602339</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1128091966028144</v>
+        <v>0.1128742979297788</v>
       </c>
       <c r="C98">
-        <v>-10.79114729771526</v>
+        <v>-12.21848618298387</v>
       </c>
       <c r="D98">
-        <v>100.2888527022847</v>
+        <v>100.1915138170161</v>
       </c>
       <c r="E98">
-        <v>52.77999999999999</v>
+        <v>54.10999999999999</v>
       </c>
       <c r="F98">
-        <v>127.68</v>
+        <v>129.01</v>
       </c>
       <c r="G98">
         <v>16.6</v>
@@ -9311,28 +9311,28 @@
         <v>18.375</v>
       </c>
       <c r="M98">
-        <v>11.4912</v>
+        <v>11.6109</v>
       </c>
       <c r="N98">
-        <v>6.883800000000001</v>
+        <v>6.764100000000001</v>
       </c>
       <c r="O98">
-        <v>1.72095</v>
+        <v>1.691025</v>
       </c>
       <c r="P98">
-        <v>5.162850000000001</v>
+        <v>5.073075000000001</v>
       </c>
       <c r="Q98">
-        <v>9.662850000000001</v>
+        <v>9.573075000000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.200229915070359</v>
+        <v>1.579976597659293</v>
       </c>
       <c r="T98">
-        <v>16.79836189434394</v>
+        <v>22.32413883327286</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.599049707602339</v>
+        <v>1.582564659070356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1128742979297788</v>
+        <v>0.1129393992567433</v>
       </c>
       <c r="C99">
-        <v>-12.21848618298387</v>
+        <v>-13.64563630008755</v>
       </c>
       <c r="D99">
-        <v>100.1915138170161</v>
+        <v>100.0943636999125</v>
       </c>
       <c r="E99">
-        <v>54.10999999999999</v>
+        <v>55.44</v>
       </c>
       <c r="F99">
-        <v>129.01</v>
+        <v>130.34</v>
       </c>
       <c r="G99">
         <v>16.6</v>
@@ -9393,28 +9393,28 @@
         <v>18.375</v>
       </c>
       <c r="M99">
-        <v>11.6109</v>
+        <v>11.7306</v>
       </c>
       <c r="N99">
-        <v>6.764100000000001</v>
+        <v>6.644400000000001</v>
       </c>
       <c r="O99">
-        <v>1.691025</v>
+        <v>1.6611</v>
       </c>
       <c r="P99">
-        <v>5.073075000000001</v>
+        <v>4.983300000000001</v>
       </c>
       <c r="Q99">
-        <v>9.573075000000001</v>
+        <v>9.4833</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.579976597659293</v>
+        <v>2.339469962837161</v>
       </c>
       <c r="T99">
-        <v>22.32413883327286</v>
+        <v>33.37569271113072</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.582564659070356</v>
+        <v>1.566416040100251</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1129393992567433</v>
+        <v>0.1130045005837077</v>
       </c>
       <c r="C100">
-        <v>-13.64563630008755</v>
+        <v>-15.07259819760819</v>
       </c>
       <c r="D100">
-        <v>100.0943636999125</v>
+        <v>99.99740180239179</v>
       </c>
       <c r="E100">
-        <v>55.44</v>
+        <v>56.76999999999998</v>
       </c>
       <c r="F100">
-        <v>130.34</v>
+        <v>131.67</v>
       </c>
       <c r="G100">
         <v>16.6</v>
@@ -9475,28 +9475,28 @@
         <v>18.375</v>
       </c>
       <c r="M100">
-        <v>11.7306</v>
+        <v>11.8503</v>
       </c>
       <c r="N100">
-        <v>6.644400000000001</v>
+        <v>6.524700000000001</v>
       </c>
       <c r="O100">
-        <v>1.6611</v>
+        <v>1.631175</v>
       </c>
       <c r="P100">
-        <v>4.983300000000001</v>
+        <v>4.893525</v>
       </c>
       <c r="Q100">
-        <v>9.4833</v>
+        <v>9.393525</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.339469962837161</v>
+        <v>4.617950058370765</v>
       </c>
       <c r="T100">
-        <v>33.37569271113072</v>
+        <v>66.53035434470428</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.566416040100251</v>
+        <v>1.550593655856814</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1130045005837077</v>
-      </c>
-      <c r="C101">
-        <v>-15.07259819760819</v>
-      </c>
-      <c r="D101">
-        <v>99.99740180239179</v>
-      </c>
-      <c r="E101">
-        <v>56.76999999999998</v>
-      </c>
-      <c r="F101">
-        <v>131.67</v>
-      </c>
-      <c r="G101">
-        <v>16.6</v>
-      </c>
-      <c r="H101">
-        <v>58.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.875</v>
-      </c>
-      <c r="K101">
-        <v>4.5</v>
-      </c>
-      <c r="L101">
-        <v>18.375</v>
-      </c>
-      <c r="M101">
-        <v>11.8503</v>
-      </c>
-      <c r="N101">
-        <v>6.524700000000001</v>
-      </c>
-      <c r="O101">
-        <v>1.631175</v>
-      </c>
-      <c r="P101">
-        <v>4.893525</v>
-      </c>
-      <c r="Q101">
-        <v>9.393525</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.617950058370765</v>
-      </c>
-      <c r="T101">
-        <v>66.53035434470428</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.0675</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.550593655856814</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
